--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -570,22 +570,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
+          <t>Deep Bay Graphite Deposit</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5996</v>
+        <v>480</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -623,14 +623,14 @@
         <v>38</v>
       </c>
       <c r="V2" t="n">
-        <v>49.56951</v>
+        <v>56.38334</v>
       </c>
       <c r="W2" t="n">
-        <v>-103.14392</v>
+        <v>-103.12501</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
         </is>
       </c>
     </row>
@@ -710,22 +710,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fond Du Lac Uranium Deposit</t>
+          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1572</v>
+        <v>5996</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uranium, Iron</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -763,14 +763,14 @@
         <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>59.30417</v>
+        <v>49.56951</v>
       </c>
       <c r="W4" t="n">
-        <v>-107.16668</v>
+        <v>-103.14392</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deep Bay Graphite Deposit</t>
+          <t>Fond Du Lac Uranium Deposit</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>1572</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Uranium, Iron</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -833,14 +833,14 @@
         <v>38</v>
       </c>
       <c r="V5" t="n">
-        <v>56.38334</v>
+        <v>59.30417</v>
       </c>
       <c r="W5" t="n">
-        <v>-103.12501</v>
+        <v>-107.16668</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
         </is>
       </c>
     </row>
@@ -850,27 +850,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canera Francis 6-36-12-15</t>
+          <t>777 Mine (Triple 7 Mine)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5553</v>
+        <v>72</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Copper, Gold, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -894,23 +894,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>50.03521</v>
+        <v>54.77497</v>
       </c>
       <c r="W6" t="n">
-        <v>-103.9312</v>
+        <v>-101.87837</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0072</t>
         </is>
       </c>
     </row>
@@ -920,11 +920,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEML et al Bigstick 6-14-13-26</t>
+          <t>Sturgeon Lake</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5551</v>
+        <v>4390</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Marl</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -964,23 +964,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>50.08028</v>
+        <v>53.39971</v>
       </c>
       <c r="W7" t="n">
-        <v>-109.45467</v>
+        <v>-106.09243</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4390</t>
         </is>
       </c>
     </row>
@@ -990,11 +990,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1A9</t>
+          <t>Lydden Lake Deposit</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5550</v>
+        <v>3676</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,14 +1043,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>50.41143</v>
+        <v>52.01647</v>
       </c>
       <c r="W8" t="n">
-        <v>-107.86354</v>
+        <v>-108.36644</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
+          <t>Bitter Lake Deposit</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5552</v>
+        <v>3673</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1113,14 +1113,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>49.34918</v>
+        <v>50.10616</v>
       </c>
       <c r="W9" t="n">
-        <v>-104.82203</v>
+        <v>-109.79816</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
         </is>
       </c>
     </row>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eins Lake</t>
+          <t>Sybouts West Deposit</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4369</v>
+        <v>3672</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1183,14 +1183,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>52.04888</v>
+        <v>49.04192</v>
       </c>
       <c r="W10" t="n">
-        <v>-108.51676</v>
+        <v>-104.53479</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sturgeon Lake</t>
+          <t>Estevan Brick Kaolin 1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4390</v>
+        <v>3849</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marl</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1244,23 +1244,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>53.39971</v>
+        <v>49.52546</v>
       </c>
       <c r="W11" t="n">
-        <v>-106.09243</v>
+        <v>-108.84275</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4390</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Redberry Lake</t>
+          <t>Wood Mountain Ridge Resource Area</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5044</v>
+        <v>3972</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1323,14 +1323,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>52.69009</v>
+        <v>49.41751</v>
       </c>
       <c r="W12" t="n">
-        <v>-107.16763</v>
+        <v>-106.3298</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Basin Lake</t>
+          <t>Estevan Brick Kaolin 2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5043</v>
+        <v>3861</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1393,14 +1393,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>52.60621</v>
+        <v>49.50293</v>
       </c>
       <c r="W13" t="n">
-        <v>-105.2732</v>
+        <v>-109.01845</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Talisman Bures 11-17-9-21</t>
+          <t>Rockglen</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5548</v>
+        <v>3976</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite, Volcanic Ash</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1463,14 +1463,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>49.73459</v>
+        <v>49.19705</v>
       </c>
       <c r="W14" t="n">
-        <v>-104.81905</v>
+        <v>-106.03823</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IAC Wilhelm 2-9-17-14</t>
+          <t>Waverly Ridge Resource Area</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5549</v>
+        <v>3973</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,14 +1533,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>50.41344</v>
+        <v>49.36742</v>
       </c>
       <c r="W15" t="n">
-        <v>-107.86864</v>
+        <v>-106.49029</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
         </is>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
+          <t>Eastend Resource Area</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5547</v>
+        <v>3866</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1603,14 +1603,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>49.01463</v>
+        <v>49.40637</v>
       </c>
       <c r="W16" t="n">
-        <v>-109.73056</v>
+        <v>-108.62578</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BA Sask Lndg Wilhelm 3-10-17-14</t>
+          <t>Estevan Brick 72H-5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4313</v>
+        <v>4078</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1673,14 +1673,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>50.41166</v>
+        <v>49.63023</v>
       </c>
       <c r="W17" t="n">
-        <v>-107.85147</v>
+        <v>-105.81014</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wood Mountain Ridge Resource Area</t>
+          <t>BA Wilhelm 1-9</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3972</v>
+        <v>4312</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1743,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="V18" t="n">
-        <v>49.41751</v>
+        <v>50.41172</v>
       </c>
       <c r="W18" t="n">
-        <v>-106.3298</v>
+        <v>-107.86309</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
         </is>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rockglen</t>
+          <t>BA Sask Lndg Wilhelm 3-10-17-14</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3976</v>
+        <v>4313</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bentonite, Volcanic Ash</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1813,14 +1813,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>49.19705</v>
+        <v>50.41166</v>
       </c>
       <c r="W19" t="n">
-        <v>-106.03823</v>
+        <v>-107.85147</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
         </is>
       </c>
     </row>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gulf Wilhelm 11-3-17-14</t>
+          <t>Basin Lake</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4311</v>
+        <v>5043</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2023,14 +2023,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>50.40418</v>
+        <v>52.60621</v>
       </c>
       <c r="W22" t="n">
-        <v>-107.84977</v>
+        <v>-105.2732</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1-9</t>
+          <t>Redberry Lake</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4312</v>
+        <v>5044</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2093,14 +2093,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>50.41172</v>
+        <v>52.69009</v>
       </c>
       <c r="W23" t="n">
-        <v>-107.86309</v>
+        <v>-107.16763</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
         </is>
       </c>
     </row>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-5</t>
+          <t>Gulf Wilhelm 11-3-17-14</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4078</v>
+        <v>4311</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,14 +2163,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>49.63023</v>
+        <v>50.40418</v>
       </c>
       <c r="W24" t="n">
-        <v>-105.81014</v>
+        <v>-107.84977</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
         </is>
       </c>
     </row>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Waverly Ridge Resource Area</t>
+          <t>Eins Lake</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3973</v>
+        <v>4369</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2233,14 +2233,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>49.36742</v>
+        <v>52.04888</v>
       </c>
       <c r="W25" t="n">
-        <v>-106.49029</v>
+        <v>-108.51676</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
         </is>
       </c>
     </row>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 2</t>
+          <t>Verlo East Deposit</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3861</v>
+        <v>3671</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2303,14 +2303,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>49.50293</v>
+        <v>50.33614</v>
       </c>
       <c r="W26" t="n">
-        <v>-109.01845</v>
+        <v>-108.45696</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eastend Resource Area</t>
+          <t>Aroma Lake Deposit</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3866</v>
+        <v>3668</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2373,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>49.40637</v>
+        <v>52.29156</v>
       </c>
       <c r="W27" t="n">
-        <v>-108.62578</v>
+        <v>-108.55453</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
         </is>
       </c>
     </row>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 1</t>
+          <t>Ingebrigt North Deposit</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3849</v>
+        <v>3669</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2443,14 +2443,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>49.52546</v>
+        <v>50.40828</v>
       </c>
       <c r="W28" t="n">
-        <v>-108.84275</v>
+        <v>-109.38439</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lydden Lake Deposit</t>
+          <t>C28 Kimberlite</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3676</v>
+        <v>2864</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2513,14 +2513,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>52.01647</v>
+        <v>53.70316</v>
       </c>
       <c r="W29" t="n">
-        <v>-108.36644</v>
+        <v>-104.85739</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verlo East Deposit</t>
+          <t>Canera Francis 6-36-12-15</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3671</v>
+        <v>5553</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2583,14 +2583,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>50.33614</v>
+        <v>50.03521</v>
       </c>
       <c r="W30" t="n">
-        <v>-108.45696</v>
+        <v>-103.9312</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bitter Lake Deposit</t>
+          <t>Axe Lake Deposit</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3673</v>
+        <v>2784</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Oil Sand</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>50.10616</v>
+        <v>57.20387</v>
       </c>
       <c r="W31" t="n">
-        <v>-109.79816</v>
+        <v>-109.9058</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sybouts West Deposit</t>
+          <t>BA Wilhelm 1A9</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3672</v>
+        <v>5550</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2723,14 +2723,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>49.04192</v>
+        <v>50.41143</v>
       </c>
       <c r="W32" t="n">
-        <v>-104.53479</v>
+        <v>-107.86354</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aroma Lake Deposit</t>
+          <t>DEML et al Bigstick 6-14-13-26</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3668</v>
+        <v>5551</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2793,14 +2793,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>52.29156</v>
+        <v>50.08028</v>
       </c>
       <c r="W33" t="n">
-        <v>-108.55453</v>
+        <v>-109.45467</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2810,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ingebrigt North Deposit</t>
+          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3669</v>
+        <v>5552</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2863,14 +2863,14 @@
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>50.40828</v>
+        <v>49.34918</v>
       </c>
       <c r="W34" t="n">
-        <v>-109.38439</v>
+        <v>-104.82203</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C28 Kimberlite</t>
+          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2864</v>
+        <v>5547</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2933,14 +2933,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>53.70316</v>
+        <v>49.01463</v>
       </c>
       <c r="W35" t="n">
-        <v>-104.85739</v>
+        <v>-109.73056</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Axe Lake Deposit</t>
+          <t>Talisman Bures 11-17-9-21</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2784</v>
+        <v>5548</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Oil Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3003,14 +3003,14 @@
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>57.20387</v>
+        <v>49.73459</v>
       </c>
       <c r="W36" t="n">
-        <v>-109.9058</v>
+        <v>-104.81905</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
         </is>
       </c>
     </row>
@@ -3020,27 +3020,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>777 Mine (Triple 7 Mine)</t>
+          <t>IAC Wilhelm 2-9-17-14</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>72</v>
+        <v>5549</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Zinc</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Advanced Exploration</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3064,23 +3064,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>54.77497</v>
+        <v>50.41344</v>
       </c>
       <c r="W37" t="n">
-        <v>-101.87837</v>
+        <v>-107.86864</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0072</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/12-25-004-09W3/00]</t>
+          <t>Willow Bunch Clinker Shale Mine</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6020</v>
+        <v>2781</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Clinker</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3143,14 +3143,14 @@
         <v>30</v>
       </c>
       <c r="V38" t="n">
-        <v>49.3267</v>
+        <v>49.32932</v>
       </c>
       <c r="W38" t="n">
-        <v>-107.10608</v>
+        <v>-105.52988</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-14-004-09W3/00]</t>
+          <t>Gollier Creek Mine</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6019</v>
+        <v>2780</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3213,14 +3213,14 @@
         <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>49.30305</v>
+        <v>49.41374</v>
       </c>
       <c r="W39" t="n">
-        <v>-107.10613</v>
+        <v>-106.24081</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truax Quarry</t>
+          <t>Helium Production Well [101/05-26-004-09W3/00]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2782</v>
+        <v>6017</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bentonite</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3283,14 +3283,14 @@
         <v>30</v>
       </c>
       <c r="V40" t="n">
-        <v>49.96019</v>
+        <v>49.32636</v>
       </c>
       <c r="W40" t="n">
-        <v>-104.81877</v>
+        <v>-107.12461</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-28-009-11W3/00]</t>
+          <t>Helium Production Well [101/16-27-005-26W3/00]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6008</v>
+        <v>6015</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3353,14 +3353,14 @@
         <v>30</v>
       </c>
       <c r="V41" t="n">
-        <v>49.76938</v>
+        <v>49.42248</v>
       </c>
       <c r="W41" t="n">
-        <v>-107.42801</v>
+        <v>-109.41729</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3440,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-21-005-27W3/00]</t>
+          <t>Truax Quarry</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6013</v>
+        <v>2782</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3493,14 +3493,14 @@
         <v>30</v>
       </c>
       <c r="V43" t="n">
-        <v>49.40655</v>
+        <v>49.96019</v>
       </c>
       <c r="W43" t="n">
-        <v>-109.5718</v>
+        <v>-104.81877</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
         </is>
       </c>
     </row>
@@ -3510,11 +3510,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Helium Production Well [103/08-04-006-26W3/02]</t>
+          <t>Helium Production Well [101/16-28-009-11W3/00]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6014</v>
+        <v>6008</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3563,14 +3563,14 @@
         <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>49.44309</v>
+        <v>49.76938</v>
       </c>
       <c r="W44" t="n">
-        <v>-109.44006</v>
+        <v>-107.42801</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/14-03-017-14W3/00]</t>
+          <t>Helium Production Well [101/09-31-003-26W3/00]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6021</v>
+        <v>6002</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3633,14 +3633,14 @@
         <v>30</v>
       </c>
       <c r="V45" t="n">
-        <v>50.41137</v>
+        <v>49.25465</v>
       </c>
       <c r="W45" t="n">
-        <v>-107.85382</v>
+        <v>-109.48226</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
         </is>
       </c>
     </row>
@@ -3650,11 +3650,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Willow Bunch Clinker Shale Mine</t>
+          <t>Helium Production Well [101/16-27-009-11W3/00]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2781</v>
+        <v>6005</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Clinker</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I46" t="b">
@@ -3703,14 +3703,14 @@
         <v>30</v>
       </c>
       <c r="V46" t="n">
-        <v>49.32932</v>
+        <v>49.77022</v>
       </c>
       <c r="W46" t="n">
-        <v>-105.52988</v>
+        <v>-107.40787</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/15-35-009-11W3/00]</t>
+          <t>Helium Production Well [101/11-34-009-11W3/00]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6010</v>
+        <v>6006</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3773,14 +3773,14 @@
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>49.78513</v>
+        <v>49.77601</v>
       </c>
       <c r="W47" t="n">
-        <v>-107.39009</v>
+        <v>-107.428</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/01-03-010-11W3/00]</t>
+          <t>Helium Production Well [101/06-30-003-26W3/00]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6007</v>
+        <v>6003</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>49.7885</v>
+        <v>49.23862</v>
       </c>
       <c r="W48" t="n">
-        <v>-107.40369</v>
+        <v>-109.49394</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
         </is>
       </c>
     </row>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-35-009-11W3/00]</t>
+          <t>Helium Production Well [102/10-09-006-22W3/00]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6009</v>
+        <v>6004</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3913,14 +3913,14 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>49.77879</v>
+        <v>49.46027</v>
       </c>
       <c r="W49" t="n">
-        <v>-107.39509</v>
+        <v>-108.90729</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/02-35-005-27W3/00]</t>
+          <t>Duncairn Quarry</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6012</v>
+        <v>4314</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Volcanic Ash</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I50" t="b">
@@ -3983,14 +3983,14 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>49.424</v>
+        <v>50.09126</v>
       </c>
       <c r="W50" t="n">
-        <v>-109.53444</v>
+        <v>-108.02814</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-34-009-11W3/00]</t>
+          <t>Fusilier North Mine</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6011</v>
+        <v>4331</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4053,14 +4053,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>49.7779</v>
+        <v>51.91661</v>
       </c>
       <c r="W51" t="n">
-        <v>-107.40814</v>
+        <v>-109.79822</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/05-26-004-09W3/00]</t>
+          <t>Ravenscrag Quarry</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6017</v>
+        <v>3865</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4123,14 +4123,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>49.32636</v>
+        <v>49.49081</v>
       </c>
       <c r="W52" t="n">
-        <v>-107.12461</v>
+        <v>-109.14115</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-15-004-09W3/00]</t>
+          <t>Ceylon Lake Deposit</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6018</v>
+        <v>3670</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4193,14 +4193,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>49.3046</v>
+        <v>49.28985</v>
       </c>
       <c r="W53" t="n">
-        <v>-107.12846</v>
+        <v>-104.70435</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-005-26W3/00]</t>
+          <t>Snakehole Lake Mine</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6015</v>
+        <v>3666</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4263,14 +4263,14 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>49.42248</v>
+        <v>50.50916</v>
       </c>
       <c r="W54" t="n">
-        <v>-109.41729</v>
+        <v>-108.47667</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
         </is>
       </c>
     </row>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Murphy Quarry</t>
+          <t>Chaplin Mine</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3856</v>
+        <v>3657</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4295,12 +4295,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4333,14 +4333,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>49.49611</v>
+        <v>50.46073</v>
       </c>
       <c r="W55" t="n">
-        <v>-108.84334</v>
+        <v>-106.66983</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Old Pearson Pit</t>
+          <t>Horseshoe Lake Mine</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3859</v>
+        <v>3659</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4403,14 +4403,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>49.50023</v>
+        <v>49.71947</v>
       </c>
       <c r="W56" t="n">
-        <v>-109.01325</v>
+        <v>-105.35516</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
         </is>
       </c>
     </row>
@@ -4420,11 +4420,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Day Quarry</t>
+          <t>Ingebrigt South Mine</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3857</v>
+        <v>3660</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4473,14 +4473,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>49.51123</v>
+        <v>50.35665</v>
       </c>
       <c r="W57" t="n">
-        <v>-108.84032</v>
+        <v>-109.32196</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
         </is>
       </c>
     </row>
@@ -4490,11 +4490,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alberta Clay Products Mine</t>
+          <t>Alsask Lake Mine</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3850</v>
+        <v>3661</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4543,14 +4543,14 @@
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>49.52784</v>
+        <v>51.33929</v>
       </c>
       <c r="W58" t="n">
-        <v>-108.83616</v>
+        <v>-109.86516</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Knolly Quarry</t>
+          <t>Sybouts East Mine</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3855</v>
+        <v>3662</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4613,14 +4613,14 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>49.46895</v>
+        <v>49.03697</v>
       </c>
       <c r="W59" t="n">
-        <v>-108.92433</v>
+        <v>-104.43359</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I-XL Industries 1 Quarry</t>
+          <t>Frederick Lake Mine</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3853</v>
+        <v>3664</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4683,14 +4683,14 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>49.46928</v>
+        <v>50.00971</v>
       </c>
       <c r="W60" t="n">
-        <v>-108.83703</v>
+        <v>-105.77947</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
         </is>
       </c>
     </row>
@@ -4700,11 +4700,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Medalta Potteries Ltd. Quarry</t>
+          <t>Helium Production Well [101/01-03-010-11W3/00]</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3852</v>
+        <v>6007</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I61" t="b">
@@ -4753,14 +4753,14 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>49.53484</v>
+        <v>49.7885</v>
       </c>
       <c r="W61" t="n">
-        <v>-108.82295</v>
+        <v>-107.40369</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 1</t>
+          <t>Helium Production Well [101/06-35-009-11W3/00]</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3689</v>
+        <v>6009</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I62" t="b">
@@ -4823,14 +4823,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>49.06449</v>
+        <v>49.77879</v>
       </c>
       <c r="W62" t="n">
-        <v>-103.06979</v>
+        <v>-107.39509</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
         </is>
       </c>
     </row>
@@ -4840,11 +4840,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dempster Clay Pit</t>
+          <t>Helium Production Well [102/15-35-009-11W3/00]</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3851</v>
+        <v>6010</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -4893,14 +4893,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>49.52823</v>
+        <v>49.78513</v>
       </c>
       <c r="W63" t="n">
-        <v>-108.84206</v>
+        <v>-107.39009</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
         </is>
       </c>
     </row>
@@ -4910,11 +4910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 2</t>
+          <t>Helium Production Well [101/16-21-005-27W3/00]</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3690</v>
+        <v>6013</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -4963,14 +4963,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>49.12208</v>
+        <v>49.40655</v>
       </c>
       <c r="W64" t="n">
-        <v>-103.07029</v>
+        <v>-109.5718</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
         </is>
       </c>
     </row>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 1</t>
+          <t>Helium Production Well [103/08-04-006-26W3/02]</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3860</v>
+        <v>6014</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -5033,14 +5033,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>49.49048</v>
+        <v>49.44309</v>
       </c>
       <c r="W65" t="n">
-        <v>-109.04754</v>
+        <v>-109.44006</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Frederick Lake Mine</t>
+          <t>Helium Production Well [101/09-34-009-11W3/00]</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3664</v>
+        <v>6011</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5103,14 +5103,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>50.00971</v>
+        <v>49.7779</v>
       </c>
       <c r="W66" t="n">
-        <v>-105.77947</v>
+        <v>-107.40814</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ceylon Lake Deposit</t>
+          <t>Helium Production Well [101/02-35-005-27W3/00]</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3670</v>
+        <v>6012</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5173,14 +5173,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>49.28985</v>
+        <v>49.424</v>
       </c>
       <c r="W67" t="n">
-        <v>-104.70435</v>
+        <v>-109.53444</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
         </is>
       </c>
     </row>
@@ -5190,11 +5190,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Snakehole Lake Mine</t>
+          <t>Murphy Quarry</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3666</v>
+        <v>3856</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5243,14 +5243,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>50.50916</v>
+        <v>49.49611</v>
       </c>
       <c r="W68" t="n">
-        <v>-108.47667</v>
+        <v>-108.84334</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
         </is>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sybouts East Mine</t>
+          <t>Plainsman Quarry 4</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3662</v>
+        <v>3864</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5313,14 +5313,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>49.03697</v>
+        <v>49.51887</v>
       </c>
       <c r="W69" t="n">
-        <v>-104.43359</v>
+        <v>-109.02092</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
         </is>
       </c>
     </row>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alsask Lake Mine</t>
+          <t>Plainsman Quarry 2</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3661</v>
+        <v>3862</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5383,14 +5383,14 @@
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>51.33929</v>
+        <v>49.49514</v>
       </c>
       <c r="W70" t="n">
-        <v>-109.86516</v>
+        <v>-109.05234</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
         </is>
       </c>
     </row>
@@ -5400,11 +5400,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gollier Creek Mine</t>
+          <t>Plainsman Quarry 3</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2780</v>
+        <v>3863</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5453,14 +5453,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>49.41374</v>
+        <v>49.51582</v>
       </c>
       <c r="W71" t="n">
-        <v>-106.24081</v>
+        <v>-109.01757</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chaplin Mine</t>
+          <t>Estevan Brick Location 1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3657</v>
+        <v>3689</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5523,14 +5523,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>50.46073</v>
+        <v>49.06449</v>
       </c>
       <c r="W72" t="n">
-        <v>-106.66983</v>
+        <v>-103.06979</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5540,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Horseshoe Lake Mine</t>
+          <t>Estevan Brick Location 2</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3659</v>
+        <v>3690</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>49.71947</v>
+        <v>49.12208</v>
       </c>
       <c r="W73" t="n">
-        <v>-105.35516</v>
+        <v>-103.07029</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ingebrigt South Mine</t>
+          <t>Alberta Clay Products Mine</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3660</v>
+        <v>3850</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5663,14 +5663,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>50.35665</v>
+        <v>49.52784</v>
       </c>
       <c r="W74" t="n">
-        <v>-109.32196</v>
+        <v>-108.83616</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
         </is>
       </c>
     </row>
@@ -5680,11 +5680,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Old Pit Quarry</t>
+          <t>Dempster Clay Pit</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3858</v>
+        <v>3851</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5733,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>49.47594</v>
+        <v>49.52823</v>
       </c>
       <c r="W75" t="n">
-        <v>-109.01306</v>
+        <v>-108.84206</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
         </is>
       </c>
     </row>
@@ -5750,11 +5750,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 2</t>
+          <t>Helium Production Well [101/16-14-004-09W3/00]</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3862</v>
+        <v>6019</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -5803,14 +5803,14 @@
         <v>30</v>
       </c>
       <c r="V76" t="n">
-        <v>49.49514</v>
+        <v>49.30305</v>
       </c>
       <c r="W76" t="n">
-        <v>-109.05234</v>
+        <v>-107.10613</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
         </is>
       </c>
     </row>
@@ -5820,11 +5820,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 3</t>
+          <t>Helium Production Well [101/12-25-004-09W3/00]</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3863</v>
+        <v>6020</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -5873,14 +5873,14 @@
         <v>30</v>
       </c>
       <c r="V77" t="n">
-        <v>49.51582</v>
+        <v>49.3267</v>
       </c>
       <c r="W77" t="n">
-        <v>-109.01757</v>
+        <v>-107.10608</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A.P. Green Quarry</t>
+          <t>Estevan Brick 72H-1 Quarry</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4288</v>
+        <v>4074</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -5943,14 +5943,14 @@
         <v>30</v>
       </c>
       <c r="V78" t="n">
-        <v>50.09003</v>
+        <v>49.60125</v>
       </c>
       <c r="W78" t="n">
-        <v>-105.43064</v>
+        <v>-105.74607</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
         </is>
       </c>
     </row>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Duncairn Quarry</t>
+          <t>Great Lakes Ceramics Quarry</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4314</v>
+        <v>3975</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Volcanic Ash</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>30</v>
       </c>
       <c r="V79" t="n">
-        <v>50.09126</v>
+        <v>49.20355</v>
       </c>
       <c r="W79" t="n">
-        <v>-108.02814</v>
+        <v>-106.07015</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dominion Firebrick Quarry</t>
+          <t>I-XL Industries 1 Quarry</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4287</v>
+        <v>3853</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6083,14 +6083,14 @@
         <v>30</v>
       </c>
       <c r="V80" t="n">
-        <v>50.02441</v>
+        <v>49.46928</v>
       </c>
       <c r="W80" t="n">
-        <v>-105.22623</v>
+        <v>-108.83703</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fusilier North Mine</t>
+          <t>Medalta Potteries Ltd. Quarry</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4331</v>
+        <v>3852</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6153,14 +6153,14 @@
         <v>30</v>
       </c>
       <c r="V81" t="n">
-        <v>51.91661</v>
+        <v>49.53484</v>
       </c>
       <c r="W81" t="n">
-        <v>-109.79822</v>
+        <v>-108.82295</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-4 Quarry</t>
+          <t>Knolly Quarry</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4077</v>
+        <v>3855</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6223,14 +6223,14 @@
         <v>30</v>
       </c>
       <c r="V82" t="n">
-        <v>49.63087</v>
+        <v>49.46895</v>
       </c>
       <c r="W82" t="n">
-        <v>-105.78917</v>
+        <v>-108.92433</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ravenscrag Quarry</t>
+          <t>Plainsman Quarry 1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3865</v>
+        <v>3860</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6363,14 +6363,14 @@
         <v>30</v>
       </c>
       <c r="V84" t="n">
-        <v>49.49081</v>
+        <v>49.49048</v>
       </c>
       <c r="W84" t="n">
-        <v>-109.14115</v>
+        <v>-109.04754</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
         </is>
       </c>
     </row>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 4</t>
+          <t>Day Quarry</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3864</v>
+        <v>3857</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6433,14 +6433,14 @@
         <v>30</v>
       </c>
       <c r="V85" t="n">
-        <v>49.51887</v>
+        <v>49.51123</v>
       </c>
       <c r="W85" t="n">
-        <v>-109.02092</v>
+        <v>-108.84032</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6450,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Great Lakes Ceramics Quarry</t>
+          <t>Old Pit Quarry</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3975</v>
+        <v>3858</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6503,14 +6503,14 @@
         <v>30</v>
       </c>
       <c r="V86" t="n">
-        <v>49.20355</v>
+        <v>49.47594</v>
       </c>
       <c r="W86" t="n">
-        <v>-106.07015</v>
+        <v>-109.01306</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
         </is>
       </c>
     </row>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Midland Mine</t>
+          <t>Old Pearson Pit</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4073</v>
+        <v>3859</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6573,14 +6573,14 @@
         <v>30</v>
       </c>
       <c r="V87" t="n">
-        <v>49.4577</v>
+        <v>49.50023</v>
       </c>
       <c r="W87" t="n">
-        <v>-105.64778</v>
+        <v>-109.01325</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVE Mankota 10-3-5-8</t>
+          <t>CVE Mankota 12-10-5-8</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6643,14 +6643,14 @@
         <v>30</v>
       </c>
       <c r="V88" t="n">
-        <v>49.3569</v>
+        <v>49.37059</v>
       </c>
       <c r="W88" t="n">
-        <v>-107.00032</v>
+        <v>-107.01199</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVE Mankota 12-10-5-8</t>
+          <t>Wapaw Bay Lignite-Leonardite Deposits</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4063</v>
+        <v>671</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Leonardite, Coal</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -6704,23 +6704,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T89" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U89" t="n">
         <v>30</v>
       </c>
       <c r="V89" t="n">
-        <v>49.37059</v>
+        <v>54.86112</v>
       </c>
       <c r="W89" t="n">
-        <v>-107.01199</v>
+        <v>-104.66112</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6730,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-1 Quarry</t>
+          <t>Midland Mine</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6783,14 +6783,14 @@
         <v>30</v>
       </c>
       <c r="V90" t="n">
-        <v>49.60125</v>
+        <v>49.4577</v>
       </c>
       <c r="W90" t="n">
-        <v>-105.74607</v>
+        <v>-105.64778</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
         </is>
       </c>
     </row>
@@ -6800,11 +6800,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-009-11W3/00]</t>
+          <t>CVE Mankota 10-3-5-8</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6005</v>
+        <v>4064</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -6853,14 +6853,14 @@
         <v>30</v>
       </c>
       <c r="V91" t="n">
-        <v>49.77022</v>
+        <v>49.3569</v>
       </c>
       <c r="W91" t="n">
-        <v>-107.40787</v>
+        <v>-107.00032</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
         </is>
       </c>
     </row>
@@ -6870,11 +6870,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/10-09-006-22W3/00]</t>
+          <t>Helium Production Well [101/14-03-017-14W3/00]</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6004</v>
+        <v>6021</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -6923,14 +6923,14 @@
         <v>30</v>
       </c>
       <c r="V92" t="n">
-        <v>49.46027</v>
+        <v>50.41137</v>
       </c>
       <c r="W92" t="n">
-        <v>-108.90729</v>
+        <v>-107.85382</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
         </is>
       </c>
     </row>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-30-003-26W3/00]</t>
+          <t>Helium Production Well [101/16-15-004-09W3/00]</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6003</v>
+        <v>6018</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -6993,14 +6993,14 @@
         <v>30</v>
       </c>
       <c r="V93" t="n">
-        <v>49.23862</v>
+        <v>49.3046</v>
       </c>
       <c r="W93" t="n">
-        <v>-109.49394</v>
+        <v>-107.12846</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-31-003-26W3/00]</t>
+          <t>Estevan Brick 72H-3 Quarry</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6002</v>
+        <v>4076</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7063,14 +7063,14 @@
         <v>30</v>
       </c>
       <c r="V94" t="n">
-        <v>49.25465</v>
+        <v>49.58841</v>
       </c>
       <c r="W94" t="n">
-        <v>-109.48226</v>
+        <v>-105.79049</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/11-34-009-11W3/00]</t>
+          <t>Estevan Brick 72H-4 Quarry</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6006</v>
+        <v>4077</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7133,14 +7133,14 @@
         <v>30</v>
       </c>
       <c r="V95" t="n">
-        <v>49.77601</v>
+        <v>49.63087</v>
       </c>
       <c r="W95" t="n">
-        <v>-107.428</v>
+        <v>-105.78917</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
         </is>
       </c>
     </row>
@@ -7220,11 +7220,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-3 Quarry</t>
+          <t>Dominion Firebrick Quarry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4076</v>
+        <v>4287</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7273,14 +7273,14 @@
         <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>49.58841</v>
+        <v>50.02441</v>
       </c>
       <c r="W97" t="n">
-        <v>-105.79049</v>
+        <v>-105.22623</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
         </is>
       </c>
     </row>
@@ -7290,11 +7290,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wapaw Bay Lignite-Leonardite Deposits</t>
+          <t>A.P. Green Quarry</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>671</v>
+        <v>4288</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leonardite, Coal</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7334,23 +7334,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>54.86112</v>
+        <v>50.09003</v>
       </c>
       <c r="W98" t="n">
-        <v>-104.66112</v>
+        <v>-105.43064</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
         </is>
       </c>
     </row>

--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -570,22 +570,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deep Bay Graphite Deposit</t>
+          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>480</v>
+        <v>5996</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -623,14 +623,14 @@
         <v>38</v>
       </c>
       <c r="V2" t="n">
-        <v>56.38334</v>
+        <v>49.56951</v>
       </c>
       <c r="W2" t="n">
-        <v>-103.12501</v>
+        <v>-103.14392</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
         </is>
       </c>
     </row>
@@ -710,22 +710,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
+          <t>Fond Du Lac Uranium Deposit</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5996</v>
+        <v>1572</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -763,14 +763,14 @@
         <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>49.56951</v>
+        <v>59.30417</v>
       </c>
       <c r="W4" t="n">
-        <v>-103.14392</v>
+        <v>-107.16668</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fond Du Lac Uranium Deposit</t>
+          <t>Deep Bay Graphite Deposit</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1572</v>
+        <v>480</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Uranium, Iron</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -833,14 +833,14 @@
         <v>38</v>
       </c>
       <c r="V5" t="n">
-        <v>59.30417</v>
+        <v>56.38334</v>
       </c>
       <c r="W5" t="n">
-        <v>-107.16668</v>
+        <v>-103.12501</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
         </is>
       </c>
     </row>
@@ -850,27 +850,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>777 Mine (Triple 7 Mine)</t>
+          <t>Canera Francis 6-36-12-15</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>5553</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Zinc</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Advanced Exploration</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -894,23 +894,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>54.77497</v>
+        <v>50.03521</v>
       </c>
       <c r="W6" t="n">
-        <v>-101.87837</v>
+        <v>-103.9312</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0072</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
         </is>
       </c>
     </row>
@@ -920,11 +920,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sturgeon Lake</t>
+          <t>DEML et al Bigstick 6-14-13-26</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4390</v>
+        <v>5551</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Marl</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -964,23 +964,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>53.39971</v>
+        <v>50.08028</v>
       </c>
       <c r="W7" t="n">
-        <v>-106.09243</v>
+        <v>-109.45467</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4390</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
         </is>
       </c>
     </row>
@@ -990,11 +990,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lydden Lake Deposit</t>
+          <t>BA Wilhelm 1A9</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3676</v>
+        <v>5550</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,14 +1043,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>52.01647</v>
+        <v>50.41143</v>
       </c>
       <c r="W8" t="n">
-        <v>-108.36644</v>
+        <v>-107.86354</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bitter Lake Deposit</t>
+          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3673</v>
+        <v>5552</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1113,14 +1113,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>50.10616</v>
+        <v>49.34918</v>
       </c>
       <c r="W9" t="n">
-        <v>-109.79816</v>
+        <v>-104.82203</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
         </is>
       </c>
     </row>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sybouts West Deposit</t>
+          <t>Eins Lake</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3672</v>
+        <v>4369</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1183,14 +1183,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>49.04192</v>
+        <v>52.04888</v>
       </c>
       <c r="W10" t="n">
-        <v>-104.53479</v>
+        <v>-108.51676</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 1</t>
+          <t>Sturgeon Lake</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3849</v>
+        <v>4390</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Marl</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1244,23 +1244,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>49.52546</v>
+        <v>53.39971</v>
       </c>
       <c r="W11" t="n">
-        <v>-108.84275</v>
+        <v>-106.09243</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4390</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wood Mountain Ridge Resource Area</t>
+          <t>Redberry Lake</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3972</v>
+        <v>5044</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1323,14 +1323,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>49.41751</v>
+        <v>52.69009</v>
       </c>
       <c r="W12" t="n">
-        <v>-106.3298</v>
+        <v>-107.16763</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 2</t>
+          <t>Basin Lake</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3861</v>
+        <v>5043</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1393,14 +1393,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>49.50293</v>
+        <v>52.60621</v>
       </c>
       <c r="W13" t="n">
-        <v>-109.01845</v>
+        <v>-105.2732</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rockglen</t>
+          <t>Talisman Bures 11-17-9-21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3976</v>
+        <v>5548</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bentonite, Volcanic Ash</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1463,14 +1463,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>49.19705</v>
+        <v>49.73459</v>
       </c>
       <c r="W14" t="n">
-        <v>-106.03823</v>
+        <v>-104.81905</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Waverly Ridge Resource Area</t>
+          <t>IAC Wilhelm 2-9-17-14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3973</v>
+        <v>5549</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,14 +1533,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>49.36742</v>
+        <v>50.41344</v>
       </c>
       <c r="W15" t="n">
-        <v>-106.49029</v>
+        <v>-107.86864</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
         </is>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eastend Resource Area</t>
+          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3866</v>
+        <v>5547</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1603,14 +1603,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>49.40637</v>
+        <v>49.01463</v>
       </c>
       <c r="W16" t="n">
-        <v>-108.62578</v>
+        <v>-109.73056</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-5</t>
+          <t>BA Sask Lndg Wilhelm 3-10-17-14</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4078</v>
+        <v>4313</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1673,14 +1673,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>49.63023</v>
+        <v>50.41166</v>
       </c>
       <c r="W17" t="n">
-        <v>-105.81014</v>
+        <v>-107.85147</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1-9</t>
+          <t>Wood Mountain Ridge Resource Area</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4312</v>
+        <v>3972</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1743,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="V18" t="n">
-        <v>50.41172</v>
+        <v>49.41751</v>
       </c>
       <c r="W18" t="n">
-        <v>-107.86309</v>
+        <v>-106.3298</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
         </is>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BA Sask Lndg Wilhelm 3-10-17-14</t>
+          <t>Rockglen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4313</v>
+        <v>3976</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite, Volcanic Ash</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1813,14 +1813,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>50.41166</v>
+        <v>49.19705</v>
       </c>
       <c r="W19" t="n">
-        <v>-107.85147</v>
+        <v>-106.03823</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
         </is>
       </c>
     </row>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Basin Lake</t>
+          <t>Gulf Wilhelm 11-3-17-14</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5043</v>
+        <v>4311</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2023,14 +2023,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>52.60621</v>
+        <v>50.40418</v>
       </c>
       <c r="W22" t="n">
-        <v>-105.2732</v>
+        <v>-107.84977</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Redberry Lake</t>
+          <t>BA Wilhelm 1-9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5044</v>
+        <v>4312</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2093,14 +2093,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>52.69009</v>
+        <v>50.41172</v>
       </c>
       <c r="W23" t="n">
-        <v>-107.16763</v>
+        <v>-107.86309</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
         </is>
       </c>
     </row>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gulf Wilhelm 11-3-17-14</t>
+          <t>Estevan Brick 72H-5</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4311</v>
+        <v>4078</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,14 +2163,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>50.40418</v>
+        <v>49.63023</v>
       </c>
       <c r="W24" t="n">
-        <v>-107.84977</v>
+        <v>-105.81014</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
         </is>
       </c>
     </row>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Eins Lake</t>
+          <t>Waverly Ridge Resource Area</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4369</v>
+        <v>3973</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2233,14 +2233,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>52.04888</v>
+        <v>49.36742</v>
       </c>
       <c r="W25" t="n">
-        <v>-108.51676</v>
+        <v>-106.49029</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
         </is>
       </c>
     </row>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Verlo East Deposit</t>
+          <t>Estevan Brick Kaolin 2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3671</v>
+        <v>3861</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2303,14 +2303,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>50.33614</v>
+        <v>49.50293</v>
       </c>
       <c r="W26" t="n">
-        <v>-108.45696</v>
+        <v>-109.01845</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aroma Lake Deposit</t>
+          <t>Eastend Resource Area</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3668</v>
+        <v>3866</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2373,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>52.29156</v>
+        <v>49.40637</v>
       </c>
       <c r="W27" t="n">
-        <v>-108.55453</v>
+        <v>-108.62578</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
         </is>
       </c>
     </row>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ingebrigt North Deposit</t>
+          <t>Estevan Brick Kaolin 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3669</v>
+        <v>3849</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2443,14 +2443,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>50.40828</v>
+        <v>49.52546</v>
       </c>
       <c r="W28" t="n">
-        <v>-109.38439</v>
+        <v>-108.84275</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C28 Kimberlite</t>
+          <t>Lydden Lake Deposit</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2864</v>
+        <v>3676</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2513,14 +2513,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>53.70316</v>
+        <v>52.01647</v>
       </c>
       <c r="W29" t="n">
-        <v>-104.85739</v>
+        <v>-108.36644</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canera Francis 6-36-12-15</t>
+          <t>Verlo East Deposit</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5553</v>
+        <v>3671</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2583,14 +2583,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>50.03521</v>
+        <v>50.33614</v>
       </c>
       <c r="W30" t="n">
-        <v>-103.9312</v>
+        <v>-108.45696</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Axe Lake Deposit</t>
+          <t>Bitter Lake Deposit</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2784</v>
+        <v>3673</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Oil Sand</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>57.20387</v>
+        <v>50.10616</v>
       </c>
       <c r="W31" t="n">
-        <v>-109.9058</v>
+        <v>-109.79816</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1A9</t>
+          <t>Sybouts West Deposit</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5550</v>
+        <v>3672</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2723,14 +2723,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>50.41143</v>
+        <v>49.04192</v>
       </c>
       <c r="W32" t="n">
-        <v>-107.86354</v>
+        <v>-104.53479</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DEML et al Bigstick 6-14-13-26</t>
+          <t>Aroma Lake Deposit</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5551</v>
+        <v>3668</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2793,14 +2793,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>50.08028</v>
+        <v>52.29156</v>
       </c>
       <c r="W33" t="n">
-        <v>-109.45467</v>
+        <v>-108.55453</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2810,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
+          <t>Ingebrigt North Deposit</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5552</v>
+        <v>3669</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2863,14 +2863,14 @@
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>49.34918</v>
+        <v>50.40828</v>
       </c>
       <c r="W34" t="n">
-        <v>-104.82203</v>
+        <v>-109.38439</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
+          <t>C28 Kimberlite</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5547</v>
+        <v>2864</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2933,14 +2933,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>49.01463</v>
+        <v>53.70316</v>
       </c>
       <c r="W35" t="n">
-        <v>-109.73056</v>
+        <v>-104.85739</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Talisman Bures 11-17-9-21</t>
+          <t>Axe Lake Deposit</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5548</v>
+        <v>2784</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Oil Sand</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3003,14 +3003,14 @@
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>49.73459</v>
+        <v>57.20387</v>
       </c>
       <c r="W36" t="n">
-        <v>-104.81905</v>
+        <v>-109.9058</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
         </is>
       </c>
     </row>
@@ -3020,27 +3020,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IAC Wilhelm 2-9-17-14</t>
+          <t>777 Mine (Triple 7 Mine)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5549</v>
+        <v>72</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Copper, Gold, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3064,23 +3064,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U37" t="n">
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>50.41344</v>
+        <v>54.77497</v>
       </c>
       <c r="W37" t="n">
-        <v>-107.86864</v>
+        <v>-101.87837</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0072</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Willow Bunch Clinker Shale Mine</t>
+          <t>Helium Production Well [101/12-25-004-09W3/00]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2781</v>
+        <v>6020</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3105,12 +3105,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Clinker</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3143,14 +3143,14 @@
         <v>30</v>
       </c>
       <c r="V38" t="n">
-        <v>49.32932</v>
+        <v>49.3267</v>
       </c>
       <c r="W38" t="n">
-        <v>-105.52988</v>
+        <v>-107.10608</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gollier Creek Mine</t>
+          <t>Helium Production Well [101/16-14-004-09W3/00]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2780</v>
+        <v>6019</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3175,12 +3175,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3213,14 +3213,14 @@
         <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>49.41374</v>
+        <v>49.30305</v>
       </c>
       <c r="W39" t="n">
-        <v>-106.24081</v>
+        <v>-107.10613</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/05-26-004-09W3/00]</t>
+          <t>Truax Quarry</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6017</v>
+        <v>2782</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3283,14 +3283,14 @@
         <v>30</v>
       </c>
       <c r="V40" t="n">
-        <v>49.32636</v>
+        <v>49.96019</v>
       </c>
       <c r="W40" t="n">
-        <v>-107.12461</v>
+        <v>-104.81877</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-005-26W3/00]</t>
+          <t>Helium Production Well [101/16-28-009-11W3/00]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6015</v>
+        <v>6008</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3353,14 +3353,14 @@
         <v>30</v>
       </c>
       <c r="V41" t="n">
-        <v>49.42248</v>
+        <v>49.76938</v>
       </c>
       <c r="W41" t="n">
-        <v>-109.41729</v>
+        <v>-107.42801</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3440,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Truax Quarry</t>
+          <t>Helium Production Well [101/16-21-005-27W3/00]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2782</v>
+        <v>6013</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bentonite</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3493,14 +3493,14 @@
         <v>30</v>
       </c>
       <c r="V43" t="n">
-        <v>49.96019</v>
+        <v>49.40655</v>
       </c>
       <c r="W43" t="n">
-        <v>-104.81877</v>
+        <v>-109.5718</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
         </is>
       </c>
     </row>
@@ -3510,11 +3510,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-28-009-11W3/00]</t>
+          <t>Helium Production Well [103/08-04-006-26W3/02]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6008</v>
+        <v>6014</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3563,14 +3563,14 @@
         <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>49.76938</v>
+        <v>49.44309</v>
       </c>
       <c r="W44" t="n">
-        <v>-107.42801</v>
+        <v>-109.44006</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-31-003-26W3/00]</t>
+          <t>Helium Production Well [101/14-03-017-14W3/00]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6002</v>
+        <v>6021</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3633,14 +3633,14 @@
         <v>30</v>
       </c>
       <c r="V45" t="n">
-        <v>49.25465</v>
+        <v>50.41137</v>
       </c>
       <c r="W45" t="n">
-        <v>-109.48226</v>
+        <v>-107.85382</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
         </is>
       </c>
     </row>
@@ -3650,11 +3650,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-009-11W3/00]</t>
+          <t>Willow Bunch Clinker Shale Mine</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6005</v>
+        <v>2781</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Clinker</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I46" t="b">
@@ -3703,14 +3703,14 @@
         <v>30</v>
       </c>
       <c r="V46" t="n">
-        <v>49.77022</v>
+        <v>49.32932</v>
       </c>
       <c r="W46" t="n">
-        <v>-107.40787</v>
+        <v>-105.52988</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/11-34-009-11W3/00]</t>
+          <t>Helium Production Well [102/15-35-009-11W3/00]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6006</v>
+        <v>6010</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3773,14 +3773,14 @@
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>49.77601</v>
+        <v>49.78513</v>
       </c>
       <c r="W47" t="n">
-        <v>-107.428</v>
+        <v>-107.39009</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-30-003-26W3/00]</t>
+          <t>Helium Production Well [101/01-03-010-11W3/00]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6003</v>
+        <v>6007</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>49.23862</v>
+        <v>49.7885</v>
       </c>
       <c r="W48" t="n">
-        <v>-109.49394</v>
+        <v>-107.40369</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
         </is>
       </c>
     </row>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/10-09-006-22W3/00]</t>
+          <t>Helium Production Well [101/06-35-009-11W3/00]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6004</v>
+        <v>6009</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3913,14 +3913,14 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>49.46027</v>
+        <v>49.77879</v>
       </c>
       <c r="W49" t="n">
-        <v>-108.90729</v>
+        <v>-107.39509</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Duncairn Quarry</t>
+          <t>Helium Production Well [101/02-35-005-27W3/00]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4314</v>
+        <v>6012</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Volcanic Ash</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I50" t="b">
@@ -3983,14 +3983,14 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>50.09126</v>
+        <v>49.424</v>
       </c>
       <c r="W50" t="n">
-        <v>-108.02814</v>
+        <v>-109.53444</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fusilier North Mine</t>
+          <t>Helium Production Well [101/09-34-009-11W3/00]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4331</v>
+        <v>6011</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -4053,14 +4053,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>51.91661</v>
+        <v>49.7779</v>
       </c>
       <c r="W51" t="n">
-        <v>-109.79822</v>
+        <v>-107.40814</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ravenscrag Quarry</t>
+          <t>Helium Production Well [101/05-26-004-09W3/00]</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3865</v>
+        <v>6017</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4123,14 +4123,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>49.49081</v>
+        <v>49.32636</v>
       </c>
       <c r="W52" t="n">
-        <v>-109.14115</v>
+        <v>-107.12461</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ceylon Lake Deposit</t>
+          <t>Helium Production Well [101/16-15-004-09W3/00]</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3670</v>
+        <v>6018</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I53" t="b">
@@ -4193,14 +4193,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>49.28985</v>
+        <v>49.3046</v>
       </c>
       <c r="W53" t="n">
-        <v>-104.70435</v>
+        <v>-107.12846</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Snakehole Lake Mine</t>
+          <t>Helium Production Well [101/16-27-005-26W3/00]</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3666</v>
+        <v>6015</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4263,14 +4263,14 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>50.50916</v>
+        <v>49.42248</v>
       </c>
       <c r="W54" t="n">
-        <v>-108.47667</v>
+        <v>-109.41729</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
         </is>
       </c>
     </row>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chaplin Mine</t>
+          <t>Murphy Quarry</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3657</v>
+        <v>3856</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4295,12 +4295,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4333,14 +4333,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>50.46073</v>
+        <v>49.49611</v>
       </c>
       <c r="W55" t="n">
-        <v>-106.66983</v>
+        <v>-108.84334</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Horseshoe Lake Mine</t>
+          <t>Old Pearson Pit</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3659</v>
+        <v>3859</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4403,14 +4403,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>49.71947</v>
+        <v>49.50023</v>
       </c>
       <c r="W56" t="n">
-        <v>-105.35516</v>
+        <v>-109.01325</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
         </is>
       </c>
     </row>
@@ -4420,11 +4420,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ingebrigt South Mine</t>
+          <t>Day Quarry</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3660</v>
+        <v>3857</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4473,14 +4473,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>50.35665</v>
+        <v>49.51123</v>
       </c>
       <c r="W57" t="n">
-        <v>-109.32196</v>
+        <v>-108.84032</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
         </is>
       </c>
     </row>
@@ -4490,11 +4490,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alsask Lake Mine</t>
+          <t>Alberta Clay Products Mine</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3661</v>
+        <v>3850</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4543,14 +4543,14 @@
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>51.33929</v>
+        <v>49.52784</v>
       </c>
       <c r="W58" t="n">
-        <v>-109.86516</v>
+        <v>-108.83616</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sybouts East Mine</t>
+          <t>Knolly Quarry</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3662</v>
+        <v>3855</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4613,14 +4613,14 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>49.03697</v>
+        <v>49.46895</v>
       </c>
       <c r="W59" t="n">
-        <v>-104.43359</v>
+        <v>-108.92433</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frederick Lake Mine</t>
+          <t>I-XL Industries 1 Quarry</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3664</v>
+        <v>3853</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4683,14 +4683,14 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>50.00971</v>
+        <v>49.46928</v>
       </c>
       <c r="W60" t="n">
-        <v>-105.77947</v>
+        <v>-108.83703</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
         </is>
       </c>
     </row>
@@ -4700,11 +4700,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/01-03-010-11W3/00]</t>
+          <t>Medalta Potteries Ltd. Quarry</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6007</v>
+        <v>3852</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I61" t="b">
@@ -4753,14 +4753,14 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>49.7885</v>
+        <v>49.53484</v>
       </c>
       <c r="W61" t="n">
-        <v>-107.40369</v>
+        <v>-108.82295</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-35-009-11W3/00]</t>
+          <t>Estevan Brick Location 1</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6009</v>
+        <v>3689</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4785,12 +4785,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I62" t="b">
@@ -4823,14 +4823,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>49.77879</v>
+        <v>49.06449</v>
       </c>
       <c r="W62" t="n">
-        <v>-107.39509</v>
+        <v>-103.06979</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
         </is>
       </c>
     </row>
@@ -4840,11 +4840,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/15-35-009-11W3/00]</t>
+          <t>Dempster Clay Pit</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6010</v>
+        <v>3851</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -4893,14 +4893,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>49.78513</v>
+        <v>49.52823</v>
       </c>
       <c r="W63" t="n">
-        <v>-107.39009</v>
+        <v>-108.84206</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
         </is>
       </c>
     </row>
@@ -4910,11 +4910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-21-005-27W3/00]</t>
+          <t>Estevan Brick Location 2</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6013</v>
+        <v>3690</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I64" t="b">
@@ -4963,14 +4963,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>49.40655</v>
+        <v>49.12208</v>
       </c>
       <c r="W64" t="n">
-        <v>-109.5718</v>
+        <v>-103.07029</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
         </is>
       </c>
     </row>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Helium Production Well [103/08-04-006-26W3/02]</t>
+          <t>Plainsman Quarry 1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6014</v>
+        <v>3860</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -5033,14 +5033,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>49.44309</v>
+        <v>49.49048</v>
       </c>
       <c r="W65" t="n">
-        <v>-109.44006</v>
+        <v>-109.04754</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-34-009-11W3/00]</t>
+          <t>Frederick Lake Mine</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6011</v>
+        <v>3664</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5065,12 +5065,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -5103,14 +5103,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>49.7779</v>
+        <v>50.00971</v>
       </c>
       <c r="W66" t="n">
-        <v>-107.40814</v>
+        <v>-105.77947</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/02-35-005-27W3/00]</t>
+          <t>Ceylon Lake Deposit</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6012</v>
+        <v>3670</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -5173,14 +5173,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>49.424</v>
+        <v>49.28985</v>
       </c>
       <c r="W67" t="n">
-        <v>-109.53444</v>
+        <v>-104.70435</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
         </is>
       </c>
     </row>
@@ -5190,11 +5190,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Murphy Quarry</t>
+          <t>Snakehole Lake Mine</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3856</v>
+        <v>3666</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5243,14 +5243,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>49.49611</v>
+        <v>50.50916</v>
       </c>
       <c r="W68" t="n">
-        <v>-108.84334</v>
+        <v>-108.47667</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
         </is>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 4</t>
+          <t>Sybouts East Mine</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3864</v>
+        <v>3662</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5313,14 +5313,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>49.51887</v>
+        <v>49.03697</v>
       </c>
       <c r="W69" t="n">
-        <v>-109.02092</v>
+        <v>-104.43359</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
         </is>
       </c>
     </row>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 2</t>
+          <t>Alsask Lake Mine</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3862</v>
+        <v>3661</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5383,14 +5383,14 @@
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>49.49514</v>
+        <v>51.33929</v>
       </c>
       <c r="W70" t="n">
-        <v>-109.05234</v>
+        <v>-109.86516</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
         </is>
       </c>
     </row>
@@ -5400,11 +5400,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 3</t>
+          <t>Gollier Creek Mine</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3863</v>
+        <v>2780</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5453,14 +5453,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>49.51582</v>
+        <v>49.41374</v>
       </c>
       <c r="W71" t="n">
-        <v>-109.01757</v>
+        <v>-106.24081</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 1</t>
+          <t>Chaplin Mine</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3689</v>
+        <v>3657</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5523,14 +5523,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>49.06449</v>
+        <v>50.46073</v>
       </c>
       <c r="W72" t="n">
-        <v>-103.06979</v>
+        <v>-106.66983</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5540,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 2</t>
+          <t>Horseshoe Lake Mine</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3690</v>
+        <v>3659</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>49.12208</v>
+        <v>49.71947</v>
       </c>
       <c r="W73" t="n">
-        <v>-103.07029</v>
+        <v>-105.35516</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alberta Clay Products Mine</t>
+          <t>Ingebrigt South Mine</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3850</v>
+        <v>3660</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5663,14 +5663,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>49.52784</v>
+        <v>50.35665</v>
       </c>
       <c r="W74" t="n">
-        <v>-108.83616</v>
+        <v>-109.32196</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
         </is>
       </c>
     </row>
@@ -5680,11 +5680,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dempster Clay Pit</t>
+          <t>Old Pit Quarry</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3851</v>
+        <v>3858</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5733,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>49.52823</v>
+        <v>49.47594</v>
       </c>
       <c r="W75" t="n">
-        <v>-108.84206</v>
+        <v>-109.01306</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
         </is>
       </c>
     </row>
@@ -5750,11 +5750,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-14-004-09W3/00]</t>
+          <t>Plainsman Quarry 2</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6019</v>
+        <v>3862</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -5803,14 +5803,14 @@
         <v>30</v>
       </c>
       <c r="V76" t="n">
-        <v>49.30305</v>
+        <v>49.49514</v>
       </c>
       <c r="W76" t="n">
-        <v>-107.10613</v>
+        <v>-109.05234</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
         </is>
       </c>
     </row>
@@ -5820,11 +5820,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/12-25-004-09W3/00]</t>
+          <t>Plainsman Quarry 3</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6020</v>
+        <v>3863</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -5873,14 +5873,14 @@
         <v>30</v>
       </c>
       <c r="V77" t="n">
-        <v>49.3267</v>
+        <v>49.51582</v>
       </c>
       <c r="W77" t="n">
-        <v>-107.10608</v>
+        <v>-109.01757</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-1 Quarry</t>
+          <t>A.P. Green Quarry</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4074</v>
+        <v>4288</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -5943,14 +5943,14 @@
         <v>30</v>
       </c>
       <c r="V78" t="n">
-        <v>49.60125</v>
+        <v>50.09003</v>
       </c>
       <c r="W78" t="n">
-        <v>-105.74607</v>
+        <v>-105.43064</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
         </is>
       </c>
     </row>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Great Lakes Ceramics Quarry</t>
+          <t>Duncairn Quarry</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3975</v>
+        <v>4314</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Volcanic Ash</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>30</v>
       </c>
       <c r="V79" t="n">
-        <v>49.20355</v>
+        <v>50.09126</v>
       </c>
       <c r="W79" t="n">
-        <v>-106.07015</v>
+        <v>-108.02814</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I-XL Industries 1 Quarry</t>
+          <t>Dominion Firebrick Quarry</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3853</v>
+        <v>4287</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6083,14 +6083,14 @@
         <v>30</v>
       </c>
       <c r="V80" t="n">
-        <v>49.46928</v>
+        <v>50.02441</v>
       </c>
       <c r="W80" t="n">
-        <v>-108.83703</v>
+        <v>-105.22623</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Medalta Potteries Ltd. Quarry</t>
+          <t>Fusilier North Mine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3852</v>
+        <v>4331</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6153,14 +6153,14 @@
         <v>30</v>
       </c>
       <c r="V81" t="n">
-        <v>49.53484</v>
+        <v>51.91661</v>
       </c>
       <c r="W81" t="n">
-        <v>-108.82295</v>
+        <v>-109.79822</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Knolly Quarry</t>
+          <t>Estevan Brick 72H-4 Quarry</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3855</v>
+        <v>4077</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6223,14 +6223,14 @@
         <v>30</v>
       </c>
       <c r="V82" t="n">
-        <v>49.46895</v>
+        <v>49.63087</v>
       </c>
       <c r="W82" t="n">
-        <v>-108.92433</v>
+        <v>-105.78917</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 1</t>
+          <t>Ravenscrag Quarry</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3860</v>
+        <v>3865</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6363,14 +6363,14 @@
         <v>30</v>
       </c>
       <c r="V84" t="n">
-        <v>49.49048</v>
+        <v>49.49081</v>
       </c>
       <c r="W84" t="n">
-        <v>-109.04754</v>
+        <v>-109.14115</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
         </is>
       </c>
     </row>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Day Quarry</t>
+          <t>Plainsman Quarry 4</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3857</v>
+        <v>3864</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6433,14 +6433,14 @@
         <v>30</v>
       </c>
       <c r="V85" t="n">
-        <v>49.51123</v>
+        <v>49.51887</v>
       </c>
       <c r="W85" t="n">
-        <v>-108.84032</v>
+        <v>-109.02092</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6450,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Old Pit Quarry</t>
+          <t>Great Lakes Ceramics Quarry</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3858</v>
+        <v>3975</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6503,14 +6503,14 @@
         <v>30</v>
       </c>
       <c r="V86" t="n">
-        <v>49.47594</v>
+        <v>49.20355</v>
       </c>
       <c r="W86" t="n">
-        <v>-109.01306</v>
+        <v>-106.07015</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
         </is>
       </c>
     </row>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Old Pearson Pit</t>
+          <t>Midland Mine</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3859</v>
+        <v>4073</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6573,14 +6573,14 @@
         <v>30</v>
       </c>
       <c r="V87" t="n">
-        <v>49.50023</v>
+        <v>49.4577</v>
       </c>
       <c r="W87" t="n">
-        <v>-109.01325</v>
+        <v>-105.64778</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVE Mankota 12-10-5-8</t>
+          <t>CVE Mankota 10-3-5-8</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6643,14 +6643,14 @@
         <v>30</v>
       </c>
       <c r="V88" t="n">
-        <v>49.37059</v>
+        <v>49.3569</v>
       </c>
       <c r="W88" t="n">
-        <v>-107.01199</v>
+        <v>-107.00032</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wapaw Bay Lignite-Leonardite Deposits</t>
+          <t>CVE Mankota 12-10-5-8</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>671</v>
+        <v>4063</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6675,12 +6675,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leonardite, Coal</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -6704,23 +6704,23 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T89" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U89" t="n">
         <v>30</v>
       </c>
       <c r="V89" t="n">
-        <v>54.86112</v>
+        <v>49.37059</v>
       </c>
       <c r="W89" t="n">
-        <v>-104.66112</v>
+        <v>-107.01199</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6730,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Midland Mine</t>
+          <t>Estevan Brick 72H-1 Quarry</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6783,14 +6783,14 @@
         <v>30</v>
       </c>
       <c r="V90" t="n">
-        <v>49.4577</v>
+        <v>49.60125</v>
       </c>
       <c r="W90" t="n">
-        <v>-105.64778</v>
+        <v>-105.74607</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
         </is>
       </c>
     </row>
@@ -6800,11 +6800,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVE Mankota 10-3-5-8</t>
+          <t>Helium Production Well [101/16-27-009-11W3/00]</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4064</v>
+        <v>6005</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -6853,14 +6853,14 @@
         <v>30</v>
       </c>
       <c r="V91" t="n">
-        <v>49.3569</v>
+        <v>49.77022</v>
       </c>
       <c r="W91" t="n">
-        <v>-107.00032</v>
+        <v>-107.40787</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
         </is>
       </c>
     </row>
@@ -6870,11 +6870,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/14-03-017-14W3/00]</t>
+          <t>Helium Production Well [102/10-09-006-22W3/00]</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6021</v>
+        <v>6004</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -6923,14 +6923,14 @@
         <v>30</v>
       </c>
       <c r="V92" t="n">
-        <v>50.41137</v>
+        <v>49.46027</v>
       </c>
       <c r="W92" t="n">
-        <v>-107.85382</v>
+        <v>-108.90729</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
         </is>
       </c>
     </row>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-15-004-09W3/00]</t>
+          <t>Helium Production Well [101/06-30-003-26W3/00]</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6018</v>
+        <v>6003</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -6993,14 +6993,14 @@
         <v>30</v>
       </c>
       <c r="V93" t="n">
-        <v>49.3046</v>
+        <v>49.23862</v>
       </c>
       <c r="W93" t="n">
-        <v>-107.12846</v>
+        <v>-109.49394</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-3 Quarry</t>
+          <t>Helium Production Well [101/09-31-003-26W3/00]</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4076</v>
+        <v>6002</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7063,14 +7063,14 @@
         <v>30</v>
       </c>
       <c r="V94" t="n">
-        <v>49.58841</v>
+        <v>49.25465</v>
       </c>
       <c r="W94" t="n">
-        <v>-105.79049</v>
+        <v>-109.48226</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-4 Quarry</t>
+          <t>Helium Production Well [101/11-34-009-11W3/00]</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4077</v>
+        <v>6006</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7133,14 +7133,14 @@
         <v>30</v>
       </c>
       <c r="V95" t="n">
-        <v>49.63087</v>
+        <v>49.77601</v>
       </c>
       <c r="W95" t="n">
-        <v>-105.78917</v>
+        <v>-107.428</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
         </is>
       </c>
     </row>
@@ -7220,11 +7220,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dominion Firebrick Quarry</t>
+          <t>Estevan Brick 72H-3 Quarry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4287</v>
+        <v>4076</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7273,14 +7273,14 @@
         <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>50.02441</v>
+        <v>49.58841</v>
       </c>
       <c r="W97" t="n">
-        <v>-105.22623</v>
+        <v>-105.79049</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
         </is>
       </c>
     </row>
@@ -7290,11 +7290,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A.P. Green Quarry</t>
+          <t>Wapaw Bay Lignite-Leonardite Deposits</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4288</v>
+        <v>671</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Leonardite, Coal</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7334,23 +7334,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T98" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>50.09003</v>
+        <v>54.86112</v>
       </c>
       <c r="W98" t="n">
-        <v>-105.43064</v>
+        <v>-104.66112</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
         </is>
       </c>
     </row>

--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X100"/>
+  <dimension ref="A1:X112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Prefeasibility</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -710,22 +710,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fond Du Lac Uranium Deposit</t>
+          <t>Duperow Formation Lithium Exploration Well [04-15-032-23W3]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1572</v>
+        <v>6076</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uranium, Iron</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -763,14 +763,14 @@
         <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>59.30417</v>
+        <v>51.73895</v>
       </c>
       <c r="W4" t="n">
-        <v>-107.16668</v>
+        <v>-109.19123</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6076</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canera Francis 6-36-12-15</t>
+          <t>Fond Du Lac Uranium Deposit</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5553</v>
+        <v>1572</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Uranium, Iron</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -900,17 +900,17 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="V6" t="n">
-        <v>50.03521</v>
+        <v>59.30417</v>
       </c>
       <c r="W6" t="n">
-        <v>-103.9312</v>
+        <v>-107.16668</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
         </is>
       </c>
     </row>
@@ -920,11 +920,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEML et al Bigstick 6-14-13-26</t>
+          <t>Gollier Creek Mine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5551</v>
+        <v>2780</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Development</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -973,14 +973,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>50.08028</v>
+        <v>49.41374</v>
       </c>
       <c r="W7" t="n">
-        <v>-109.45467</v>
+        <v>-106.24081</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
         </is>
       </c>
     </row>
@@ -990,11 +990,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1A9</t>
+          <t>Bitter Lake Deposit</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5550</v>
+        <v>3673</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,14 +1043,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>50.41143</v>
+        <v>50.10616</v>
       </c>
       <c r="W8" t="n">
-        <v>-107.86354</v>
+        <v>-109.79816</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
+          <t>Lydden Lake Deposit</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5552</v>
+        <v>3676</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1113,14 +1113,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>49.34918</v>
+        <v>52.01647</v>
       </c>
       <c r="W9" t="n">
-        <v>-104.82203</v>
+        <v>-108.36644</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
         </is>
       </c>
     </row>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eins Lake</t>
+          <t>Estevan Brick Kaolin 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4369</v>
+        <v>3849</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1183,14 +1183,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>52.04888</v>
+        <v>49.52546</v>
       </c>
       <c r="W10" t="n">
-        <v>-108.51676</v>
+        <v>-108.84275</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sturgeon Lake</t>
+          <t>Estevan Brick Kaolin 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4390</v>
+        <v>3861</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Marl</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1244,23 +1244,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>53.39971</v>
+        <v>49.50293</v>
       </c>
       <c r="W11" t="n">
-        <v>-106.09243</v>
+        <v>-109.01845</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4390</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Redberry Lake</t>
+          <t>Wood Mountain Ridge Resource Area</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5044</v>
+        <v>3972</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1323,14 +1323,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>52.69009</v>
+        <v>49.41751</v>
       </c>
       <c r="W12" t="n">
-        <v>-107.16763</v>
+        <v>-106.3298</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Basin Lake</t>
+          <t>Waverly Ridge Resource Area</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5043</v>
+        <v>3973</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1393,14 +1393,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>52.60621</v>
+        <v>49.36742</v>
       </c>
       <c r="W13" t="n">
-        <v>-105.2732</v>
+        <v>-106.49029</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Talisman Bures 11-17-9-21</t>
+          <t>Ingebrigt North Deposit</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5548</v>
+        <v>3669</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1463,14 +1463,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>49.73459</v>
+        <v>50.40828</v>
       </c>
       <c r="W14" t="n">
-        <v>-104.81905</v>
+        <v>-109.38439</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IAC Wilhelm 2-9-17-14</t>
+          <t>Aroma Lake Deposit</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5549</v>
+        <v>3668</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,14 +1533,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>50.41344</v>
+        <v>52.29156</v>
       </c>
       <c r="W15" t="n">
-        <v>-107.86864</v>
+        <v>-108.55453</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
         </is>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
+          <t>Rockglen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5547</v>
+        <v>3976</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite, Volcanic Ash</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1603,14 +1603,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>49.01463</v>
+        <v>49.19705</v>
       </c>
       <c r="W16" t="n">
-        <v>-109.73056</v>
+        <v>-106.03823</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BA Sask Lndg Wilhelm 3-10-17-14</t>
+          <t>Estevan Brick 72H-2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4313</v>
+        <v>4075</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1673,14 +1673,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>50.41166</v>
+        <v>49.57279</v>
       </c>
       <c r="W17" t="n">
-        <v>-107.85147</v>
+        <v>-105.74453</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wood Mountain Ridge Resource Area</t>
+          <t>Estevan Brick 72H-5</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3972</v>
+        <v>4078</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1743,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="V18" t="n">
-        <v>49.41751</v>
+        <v>49.63023</v>
       </c>
       <c r="W18" t="n">
-        <v>-106.3298</v>
+        <v>-105.81014</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
         </is>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rockglen</t>
+          <t>Estevan Brick 72H-6</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3976</v>
+        <v>4079</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bentonite, Volcanic Ash</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1813,14 +1813,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>49.19705</v>
+        <v>49.61548</v>
       </c>
       <c r="W19" t="n">
-        <v>-106.03823</v>
+        <v>-105.81093</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1830,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-2</t>
+          <t>Eins Lake</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4075</v>
+        <v>4369</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1883,14 +1883,14 @@
         <v>35</v>
       </c>
       <c r="V20" t="n">
-        <v>49.57279</v>
+        <v>52.04888</v>
       </c>
       <c r="W20" t="n">
-        <v>-105.74453</v>
+        <v>-108.51676</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
         </is>
       </c>
     </row>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-6</t>
+          <t>BA Wilhelm 1-9</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4079</v>
+        <v>4312</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1953,14 +1953,14 @@
         <v>35</v>
       </c>
       <c r="V21" t="n">
-        <v>49.61548</v>
+        <v>50.41172</v>
       </c>
       <c r="W21" t="n">
-        <v>-105.81093</v>
+        <v>-107.86309</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
         </is>
       </c>
     </row>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gulf Wilhelm 11-3-17-14</t>
+          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4311</v>
+        <v>5552</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -2023,14 +2023,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>50.40418</v>
+        <v>49.34918</v>
       </c>
       <c r="W22" t="n">
-        <v>-107.84977</v>
+        <v>-104.82203</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1-9</t>
+          <t>Canera Francis 6-36-12-15</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4312</v>
+        <v>5553</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2093,14 +2093,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>50.41172</v>
+        <v>50.03521</v>
       </c>
       <c r="W23" t="n">
-        <v>-107.86309</v>
+        <v>-103.9312</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
         </is>
       </c>
     </row>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-5</t>
+          <t>DEML et al Bigstick 6-14-13-26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4078</v>
+        <v>5551</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,14 +2163,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>49.63023</v>
+        <v>50.08028</v>
       </c>
       <c r="W24" t="n">
-        <v>-105.81014</v>
+        <v>-109.45467</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
         </is>
       </c>
     </row>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Waverly Ridge Resource Area</t>
+          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3973</v>
+        <v>5547</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2233,14 +2233,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>49.36742</v>
+        <v>49.01463</v>
       </c>
       <c r="W25" t="n">
-        <v>-106.49029</v>
+        <v>-109.73056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
         </is>
       </c>
     </row>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 2</t>
+          <t>Talisman Bures 11-17-9-21</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3861</v>
+        <v>5548</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2303,14 +2303,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>49.50293</v>
+        <v>49.73459</v>
       </c>
       <c r="W26" t="n">
-        <v>-109.01845</v>
+        <v>-104.81905</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Eastend Resource Area</t>
+          <t>Redberry Lake</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3866</v>
+        <v>5044</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2373,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>49.40637</v>
+        <v>52.69009</v>
       </c>
       <c r="W27" t="n">
-        <v>-108.62578</v>
+        <v>-107.16763</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
         </is>
       </c>
     </row>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 1</t>
+          <t>Basin Lake</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3849</v>
+        <v>5043</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2443,14 +2443,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>49.52546</v>
+        <v>52.60621</v>
       </c>
       <c r="W28" t="n">
-        <v>-108.84275</v>
+        <v>-105.2732</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lydden Lake Deposit</t>
+          <t>Eastend Resource Area</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3676</v>
+        <v>3866</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2513,14 +2513,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>52.01647</v>
+        <v>49.40637</v>
       </c>
       <c r="W29" t="n">
-        <v>-108.36644</v>
+        <v>-108.62578</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bitter Lake Deposit</t>
+          <t>Sybouts West Deposit</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>50.10616</v>
+        <v>49.04192</v>
       </c>
       <c r="W31" t="n">
-        <v>-109.79816</v>
+        <v>-104.53479</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sybouts West Deposit</t>
+          <t>C28 Kimberlite</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3672</v>
+        <v>2864</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2723,14 +2723,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>49.04192</v>
+        <v>53.70316</v>
       </c>
       <c r="W32" t="n">
-        <v>-104.53479</v>
+        <v>-104.85739</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aroma Lake Deposit</t>
+          <t>Axe Lake Deposit</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3668</v>
+        <v>2784</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Oil Sand</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2793,14 +2793,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>52.29156</v>
+        <v>57.20387</v>
       </c>
       <c r="W33" t="n">
-        <v>-108.55453</v>
+        <v>-109.9058</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2810,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ingebrigt North Deposit</t>
+          <t>Souris River Formation Helium Production Well [101/15-09-005-21W3/02] (North American Helium Whitemud 15-9)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3669</v>
+        <v>6087</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -2860,17 +2860,17 @@
         <v>325</v>
       </c>
       <c r="U34" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V34" t="n">
-        <v>50.40828</v>
+        <v>49.3769</v>
       </c>
       <c r="W34" t="n">
-        <v>-109.38439</v>
+        <v>-108.76953</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6087</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C28 Kimberlite</t>
+          <t>Truax Quarry</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2864</v>
+        <v>2782</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Bentonite</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -2930,17 +2930,17 @@
         <v>325</v>
       </c>
       <c r="U35" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V35" t="n">
-        <v>53.70316</v>
+        <v>49.96019</v>
       </c>
       <c r="W35" t="n">
-        <v>-104.85739</v>
+        <v>-104.81877</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Axe Lake Deposit</t>
+          <t>Deadwood Formation Helium Production Well [101/14-09-006-22W3/00] (NAH Eastend 14-9-6-22)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2784</v>
+        <v>6085</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Oil Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -3000,17 +3000,17 @@
         <v>325</v>
       </c>
       <c r="U36" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V36" t="n">
-        <v>57.20387</v>
+        <v>49.46254</v>
       </c>
       <c r="W36" t="n">
-        <v>-109.9058</v>
+        <v>-108.90993</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6085</t>
         </is>
       </c>
     </row>
@@ -3020,27 +3020,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>777 Mine (Triple 7 Mine)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-07-016-16W3/00] (NAH Antelope Lake DD 2C14-7-1B14-7-16-16)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>72</v>
+        <v>6082</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Zinc</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3064,23 +3064,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V37" t="n">
-        <v>54.77497</v>
+        <v>50.33577</v>
       </c>
       <c r="W37" t="n">
-        <v>-101.87837</v>
+        <v>-108.19537</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0072</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6082</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/12-25-004-09W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/02-18-016-16W3/00] (NAH Antelope Lake DD 1C2-18-3D2-18-16-16)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6020</v>
+        <v>6084</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3143,14 +3143,14 @@
         <v>30</v>
       </c>
       <c r="V38" t="n">
-        <v>49.3267</v>
+        <v>50.34284</v>
       </c>
       <c r="W38" t="n">
-        <v>-107.10608</v>
+        <v>-108.18985</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6084</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-14-004-09W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/02-17-016-16W3/00] (NAH Antelope Lake DD 4A2-17-4D2-17-16-16)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6019</v>
+        <v>6083</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3213,14 +3213,14 @@
         <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>49.30305</v>
+        <v>50.342</v>
       </c>
       <c r="W39" t="n">
-        <v>-107.10613</v>
+        <v>-108.16593</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6083</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Truax Quarry</t>
+          <t>Deadwood Formation Helium Production Well [121/07-09-017-14W3/00] (Gulf Sask Landing Wilhelm 7 9 17 14)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2782</v>
+        <v>6088</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bentonite</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3283,14 +3283,14 @@
         <v>30</v>
       </c>
       <c r="V40" t="n">
-        <v>49.96019</v>
+        <v>50.41642</v>
       </c>
       <c r="W40" t="n">
-        <v>-104.81877</v>
+        <v>-107.87088</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6088</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-28-009-11W3/00]</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [101/11-34-002-26W3/04] (NAH Battle Creek DD 1C11-34-2B14-34-2-26)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6008</v>
+        <v>6086</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3353,14 +3353,14 @@
         <v>30</v>
       </c>
       <c r="V41" t="n">
-        <v>49.76938</v>
+        <v>49.17016</v>
       </c>
       <c r="W41" t="n">
-        <v>-107.42801</v>
+        <v>-109.40476</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6086</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/14-34-005-26W3/00]</t>
+          <t>Wapaw Bay Mine</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6016</v>
+        <v>671</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Leonardite, Coal (Non-Metallurgical)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3414,23 +3414,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>30</v>
       </c>
       <c r="V42" t="n">
-        <v>49.43366</v>
+        <v>54.86112</v>
       </c>
       <c r="W42" t="n">
-        <v>-109.4287</v>
+        <v>-104.66112</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3440,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-21-005-27W3/00]</t>
+          <t>Willow Bunch Clinker Shale Mine</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6013</v>
+        <v>2781</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Clinker</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3493,14 +3493,14 @@
         <v>30</v>
       </c>
       <c r="V43" t="n">
-        <v>49.40655</v>
+        <v>49.32932</v>
       </c>
       <c r="W43" t="n">
-        <v>-109.5718</v>
+        <v>-105.52988</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
         </is>
       </c>
     </row>
@@ -3510,11 +3510,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Helium Production Well [103/08-04-006-26W3/02]</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [102/03-35-005-27W3/04] (NAH Consul DD 1C2-35-2C2-35-5-27)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6014</v>
+        <v>6012</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3563,14 +3563,14 @@
         <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>49.44309</v>
+        <v>49.42389</v>
       </c>
       <c r="W44" t="n">
-        <v>-109.44006</v>
+        <v>-109.53802</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/14-03-017-14W3/00]</t>
+          <t>Souris River Formation Helium Production Well [101/16-21-005-27W3/02] (NAH Consul 16A-21-5-27)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6021</v>
+        <v>6013</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3633,14 +3633,14 @@
         <v>30</v>
       </c>
       <c r="V45" t="n">
-        <v>50.41137</v>
+        <v>49.40655</v>
       </c>
       <c r="W45" t="n">
-        <v>-107.85382</v>
+        <v>-109.5718</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
         </is>
       </c>
     </row>
@@ -3650,11 +3650,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Willow Bunch Clinker Shale Mine</t>
+          <t>Deadwood Formation Helium Production Well [103/08-04-006-26W3/02] (NAH Cypress 4C8-4-6-26)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2781</v>
+        <v>6014</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Clinker</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I46" t="b">
@@ -3703,14 +3703,14 @@
         <v>30</v>
       </c>
       <c r="V46" t="n">
-        <v>49.32932</v>
+        <v>49.44309</v>
       </c>
       <c r="W46" t="n">
-        <v>-105.52988</v>
+        <v>-109.44006</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/15-35-009-11W3/00]</t>
+          <t>Souris River Formation Helium Production Well [101/16-27-005-26W3/00] (NAH Cypress DD 1B1-34-4C16-27-5-26)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6010</v>
+        <v>6015</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3773,14 +3773,14 @@
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>49.78513</v>
+        <v>49.42103</v>
       </c>
       <c r="W47" t="n">
-        <v>-107.39009</v>
+        <v>-109.41718</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/01-03-010-11W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [102/14-34-005-26W3/00] (NAH Cypress 14-34-5-26)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6007</v>
+        <v>6016</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>49.7885</v>
+        <v>49.43366</v>
       </c>
       <c r="W48" t="n">
-        <v>-107.40369</v>
+        <v>-109.4287</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
         </is>
       </c>
     </row>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-35-009-11W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/05-26-004-09W3/00] (NAH Mankota DD 2D5-26-4C5-26-4-9)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6009</v>
+        <v>6017</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3913,14 +3913,14 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>49.77879</v>
+        <v>49.32636</v>
       </c>
       <c r="W49" t="n">
-        <v>-107.39509</v>
+        <v>-107.12461</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/02-35-005-27W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/16-15-004-09W3/00] (NAH Mankota West DD 1D16-15-2D16-15-4-9)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6012</v>
+        <v>6018</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -3983,14 +3983,14 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>49.424</v>
+        <v>49.3046</v>
       </c>
       <c r="W50" t="n">
-        <v>-109.53444</v>
+        <v>-107.12846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-34-009-11W3/00]</t>
+          <t>Souris River Formation Helium Production Well [102/10-09-006-22W3/00] (North American Helium Eastend 10B-9-6-22)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6011</v>
+        <v>6004</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4053,14 +4053,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>49.7779</v>
+        <v>49.46027</v>
       </c>
       <c r="W51" t="n">
-        <v>-107.40814</v>
+        <v>-108.90729</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/05-26-004-09W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/16-27-009-11W3/00] (NAH Cadillac 16-27-9-11W3)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6017</v>
+        <v>6005</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4123,14 +4123,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>49.32636</v>
+        <v>49.77022</v>
       </c>
       <c r="W52" t="n">
-        <v>-107.12461</v>
+        <v>-107.40787</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-15-004-09W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/11-34-009-11W3/00] (NAH Cadillac DD 4A8-33-3B11-34-9-11)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6018</v>
+        <v>6006</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4193,14 +4193,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>49.3046</v>
+        <v>49.77938</v>
       </c>
       <c r="W53" t="n">
-        <v>-107.12846</v>
+        <v>-107.42112</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-005-26W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/01-03-010-11W3/00] (NAH Cadillac DD 3C4-2-1C1-3-10-11)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6015</v>
+        <v>6007</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4263,14 +4263,14 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>49.42248</v>
+        <v>49.78761</v>
       </c>
       <c r="W54" t="n">
-        <v>-109.41729</v>
+        <v>-107.40843</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
         </is>
       </c>
     </row>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Murphy Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101/16-28-009-11W3/00] (NAH Cadillac DD 1D16-28-1D16-28-9-11)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3856</v>
+        <v>6008</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4295,12 +4295,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4333,14 +4333,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>49.49611</v>
+        <v>49.76938</v>
       </c>
       <c r="W55" t="n">
-        <v>-108.84334</v>
+        <v>-107.42801</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Old Pearson Pit</t>
+          <t>Deadwood Formation Helium Production Well [101/06-35-009-11W3/00] (NAH Cadillac DD 2A11-35-3D6-35-9-11)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3859</v>
+        <v>6009</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4365,12 +4365,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -4403,14 +4403,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>49.50023</v>
+        <v>49.77879</v>
       </c>
       <c r="W56" t="n">
-        <v>-109.01325</v>
+        <v>-107.39509</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
         </is>
       </c>
     </row>
@@ -4420,11 +4420,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Day Quarry</t>
+          <t>Deadwood Formation Helium Production Well [102/15-35-009-11W3/00] (North American Helium Ponteix 15-35-9-11)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3857</v>
+        <v>6010</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4473,14 +4473,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>49.51123</v>
+        <v>49.78513</v>
       </c>
       <c r="W57" t="n">
-        <v>-108.84032</v>
+        <v>-107.39009</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
         </is>
       </c>
     </row>
@@ -4490,11 +4490,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alberta Clay Products Mine</t>
+          <t>Deadwood Formation Helium Production Well [101/09-34-009-11W3/00] (NAH Cadillac DD 4C8-34-4B9-34-9-11)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3850</v>
+        <v>6011</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I58" t="b">
@@ -4543,14 +4543,14 @@
         <v>30</v>
       </c>
       <c r="V58" t="n">
-        <v>49.52784</v>
+        <v>49.77953</v>
       </c>
       <c r="W58" t="n">
-        <v>-108.83616</v>
+        <v>-107.40818</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6011</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Knolly Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101/06-36-003-27W3/00] (NAH Battle Creek DD 3C6-36-3B6-36-3-27W3)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3855</v>
+        <v>6081</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4575,12 +4575,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -4613,14 +4613,14 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>49.46895</v>
+        <v>49.252</v>
       </c>
       <c r="W59" t="n">
-        <v>-108.92433</v>
+        <v>-109.51999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6081</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I-XL Industries 1 Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101-10-01-004-09W3/00] (NAH Mankota DD 3C9-1-2A10-1-4-9)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3853</v>
+        <v>6079</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -4683,14 +4683,14 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>49.46928</v>
+        <v>49.26926</v>
       </c>
       <c r="W60" t="n">
-        <v>-108.83703</v>
+        <v>-107.09053</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6079</t>
         </is>
       </c>
     </row>
@@ -4700,11 +4700,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Medalta Potteries Ltd. Quarry</t>
+          <t>Duncairn Quarry</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3852</v>
+        <v>4314</v>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Volcanic Ash</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4753,14 +4753,14 @@
         <v>30</v>
       </c>
       <c r="V61" t="n">
-        <v>49.53484</v>
+        <v>50.09126</v>
       </c>
       <c r="W61" t="n">
-        <v>-108.82295</v>
+        <v>-108.02814</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 1</t>
+          <t>Deadwood Formation Helium Production Well [101/12-10-005-08W3/00] (CVE Mankota 12-10-5-8)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3689</v>
+        <v>4063</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4823,14 +4823,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>49.06449</v>
+        <v>49.37259</v>
       </c>
       <c r="W62" t="n">
-        <v>-103.06979</v>
+        <v>-107.01264</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
         </is>
       </c>
     </row>
@@ -4840,11 +4840,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dempster Clay Pit</t>
+          <t>Plainsman Quarry 2</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3851</v>
+        <v>3862</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -4893,14 +4893,14 @@
         <v>30</v>
       </c>
       <c r="V63" t="n">
-        <v>49.52823</v>
+        <v>49.49514</v>
       </c>
       <c r="W63" t="n">
-        <v>-108.84206</v>
+        <v>-109.05234</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
         </is>
       </c>
     </row>
@@ -4910,11 +4910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 2</t>
+          <t>Plainsman Quarry 3</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3690</v>
+        <v>3863</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -4963,14 +4963,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>49.12208</v>
+        <v>49.51582</v>
       </c>
       <c r="W64" t="n">
-        <v>-103.07029</v>
+        <v>-109.01757</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
         </is>
       </c>
     </row>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 1</t>
+          <t>Plainsman Quarry 4</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3860</v>
+        <v>3864</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -5033,14 +5033,14 @@
         <v>30</v>
       </c>
       <c r="V65" t="n">
-        <v>49.49048</v>
+        <v>49.51887</v>
       </c>
       <c r="W65" t="n">
-        <v>-109.04754</v>
+        <v>-109.02092</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Frederick Lake Mine</t>
+          <t>Estevan Brick 72G Quarry</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3664</v>
+        <v>3974</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5103,14 +5103,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>50.00971</v>
+        <v>49.20739</v>
       </c>
       <c r="W66" t="n">
-        <v>-105.77947</v>
+        <v>-106.06351</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ceylon Lake Deposit</t>
+          <t>Knolly Quarry</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3670</v>
+        <v>3855</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5173,14 +5173,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>49.28985</v>
+        <v>49.46895</v>
       </c>
       <c r="W67" t="n">
-        <v>-104.70435</v>
+        <v>-108.92433</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
         </is>
       </c>
     </row>
@@ -5190,11 +5190,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Snakehole Lake Mine</t>
+          <t>Murphy Quarry</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3666</v>
+        <v>3856</v>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5243,14 +5243,14 @@
         <v>30</v>
       </c>
       <c r="V68" t="n">
-        <v>50.50916</v>
+        <v>49.49611</v>
       </c>
       <c r="W68" t="n">
-        <v>-108.47667</v>
+        <v>-108.84334</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3856</t>
         </is>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sybouts East Mine</t>
+          <t>I-XL Industries 1 Quarry</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3662</v>
+        <v>3853</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5313,14 +5313,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>49.03697</v>
+        <v>49.46928</v>
       </c>
       <c r="W69" t="n">
-        <v>-104.43359</v>
+        <v>-108.83703</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
         </is>
       </c>
     </row>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alsask Lake Mine</t>
+          <t>Day Quarry</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3661</v>
+        <v>3857</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5383,14 +5383,14 @@
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>51.33929</v>
+        <v>49.51123</v>
       </c>
       <c r="W70" t="n">
-        <v>-109.86516</v>
+        <v>-108.84032</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
         </is>
       </c>
     </row>
@@ -5400,11 +5400,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gollier Creek Mine</t>
+          <t>Medalta Potteries Ltd. Quarry</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2780</v>
+        <v>3852</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
@@ -5453,14 +5453,14 @@
         <v>30</v>
       </c>
       <c r="V71" t="n">
-        <v>49.41374</v>
+        <v>49.53484</v>
       </c>
       <c r="W71" t="n">
-        <v>-106.24081</v>
+        <v>-108.82295</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3852</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chaplin Mine</t>
+          <t>Old Pit Quarry</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3657</v>
+        <v>3858</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5485,12 +5485,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -5523,14 +5523,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>50.46073</v>
+        <v>49.47594</v>
       </c>
       <c r="W72" t="n">
-        <v>-106.66983</v>
+        <v>-109.01306</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5540,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Horseshoe Lake Mine</t>
+          <t>Old Pearson Pit</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3659</v>
+        <v>3859</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>30</v>
       </c>
       <c r="V73" t="n">
-        <v>49.71947</v>
+        <v>49.50023</v>
       </c>
       <c r="W73" t="n">
-        <v>-105.35516</v>
+        <v>-109.01325</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3859</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ingebrigt South Mine</t>
+          <t>Ravenscrag Quarry</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3660</v>
+        <v>3865</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5663,14 +5663,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>50.35665</v>
+        <v>49.49081</v>
       </c>
       <c r="W74" t="n">
-        <v>-109.32196</v>
+        <v>-109.14115</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
         </is>
       </c>
     </row>
@@ -5680,11 +5680,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Old Pit Quarry</t>
+          <t>Ceylon Lake Deposit</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3858</v>
+        <v>3670</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5733,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>49.47594</v>
+        <v>49.28985</v>
       </c>
       <c r="W75" t="n">
-        <v>-109.01306</v>
+        <v>-104.70435</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
         </is>
       </c>
     </row>
@@ -5750,11 +5750,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 2</t>
+          <t>Alberta Clay Products Mine</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3862</v>
+        <v>3850</v>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
@@ -5803,14 +5803,14 @@
         <v>30</v>
       </c>
       <c r="V76" t="n">
-        <v>49.49514</v>
+        <v>49.52784</v>
       </c>
       <c r="W76" t="n">
-        <v>-109.05234</v>
+        <v>-108.83616</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3862</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3850</t>
         </is>
       </c>
     </row>
@@ -5820,11 +5820,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 3</t>
+          <t>Estevan Brick Location 2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3863</v>
+        <v>3690</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -5873,14 +5873,14 @@
         <v>30</v>
       </c>
       <c r="V77" t="n">
-        <v>49.51582</v>
+        <v>49.12208</v>
       </c>
       <c r="W77" t="n">
-        <v>-109.01757</v>
+        <v>-103.07029</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A.P. Green Quarry</t>
+          <t>Dempster Clay Pit</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4288</v>
+        <v>3851</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -5943,14 +5943,14 @@
         <v>30</v>
       </c>
       <c r="V78" t="n">
-        <v>50.09003</v>
+        <v>49.52823</v>
       </c>
       <c r="W78" t="n">
-        <v>-105.43064</v>
+        <v>-108.84206</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
         </is>
       </c>
     </row>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Duncairn Quarry</t>
+          <t>Estevan Brick Location 1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>4314</v>
+        <v>3689</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Volcanic Ash</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>30</v>
       </c>
       <c r="V79" t="n">
-        <v>50.09126</v>
+        <v>49.06449</v>
       </c>
       <c r="W79" t="n">
-        <v>-108.02814</v>
+        <v>-103.06979</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4314</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dominion Firebrick Quarry</t>
+          <t>Frederick Lake Mine</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4287</v>
+        <v>3664</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6083,14 +6083,14 @@
         <v>30</v>
       </c>
       <c r="V80" t="n">
-        <v>50.02441</v>
+        <v>50.00971</v>
       </c>
       <c r="W80" t="n">
-        <v>-105.22623</v>
+        <v>-105.77947</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fusilier North Mine</t>
+          <t>Chaplin Mine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4331</v>
+        <v>3657</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6153,14 +6153,14 @@
         <v>30</v>
       </c>
       <c r="V81" t="n">
-        <v>51.91661</v>
+        <v>50.46073</v>
       </c>
       <c r="W81" t="n">
-        <v>-109.79822</v>
+        <v>-106.66983</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-4 Quarry</t>
+          <t>Alsask Lake Mine</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4077</v>
+        <v>3661</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6223,14 +6223,14 @@
         <v>30</v>
       </c>
       <c r="V82" t="n">
-        <v>49.63087</v>
+        <v>51.33929</v>
       </c>
       <c r="W82" t="n">
-        <v>-105.78917</v>
+        <v>-109.86516</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
         </is>
       </c>
     </row>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Estevan Brick 72G Quarry</t>
+          <t>Ingebrigt South Mine</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3974</v>
+        <v>3660</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6293,14 +6293,14 @@
         <v>30</v>
       </c>
       <c r="V83" t="n">
-        <v>49.20739</v>
+        <v>50.35665</v>
       </c>
       <c r="W83" t="n">
-        <v>-106.06351</v>
+        <v>-109.32196</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ravenscrag Quarry</t>
+          <t>Horseshoe Lake Mine</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3865</v>
+        <v>3659</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6363,14 +6363,14 @@
         <v>30</v>
       </c>
       <c r="V84" t="n">
-        <v>49.49081</v>
+        <v>49.71947</v>
       </c>
       <c r="W84" t="n">
-        <v>-109.14115</v>
+        <v>-105.35516</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
         </is>
       </c>
     </row>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 4</t>
+          <t>Sybouts East Mine</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3864</v>
+        <v>3662</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6433,14 +6433,14 @@
         <v>30</v>
       </c>
       <c r="V85" t="n">
-        <v>49.51887</v>
+        <v>49.03697</v>
       </c>
       <c r="W85" t="n">
-        <v>-109.02092</v>
+        <v>-104.43359</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6450,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Great Lakes Ceramics Quarry</t>
+          <t>Snakehole Lake Mine</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3975</v>
+        <v>3666</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6503,14 +6503,14 @@
         <v>30</v>
       </c>
       <c r="V86" t="n">
-        <v>49.20355</v>
+        <v>50.50916</v>
       </c>
       <c r="W86" t="n">
-        <v>-106.07015</v>
+        <v>-108.47667</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
         </is>
       </c>
     </row>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Midland Mine</t>
+          <t>Plainsman Quarry 1</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4073</v>
+        <v>3860</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6573,14 +6573,14 @@
         <v>30</v>
       </c>
       <c r="V87" t="n">
-        <v>49.4577</v>
+        <v>49.49048</v>
       </c>
       <c r="W87" t="n">
-        <v>-105.64778</v>
+        <v>-109.04754</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVE Mankota 10-3-5-8</t>
+          <t>Deadwood Formation Helium Production Well [101/06-30-003-26W3/00] (North American Helium Battle Creek W 6-3)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4064</v>
+        <v>6003</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I88" t="b">
@@ -6643,14 +6643,14 @@
         <v>30</v>
       </c>
       <c r="V88" t="n">
-        <v>49.3569</v>
+        <v>49.23862</v>
       </c>
       <c r="W88" t="n">
-        <v>-107.00032</v>
+        <v>-109.49394</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVE Mankota 12-10-5-8</t>
+          <t>Deadwood Formation Helium Production Well [101/10-36-003-09W3/02] (NAH Mankota DD 1C14-36-3C10-36-3-9)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4063</v>
+        <v>6078</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I89" t="b">
@@ -6713,14 +6713,14 @@
         <v>30</v>
       </c>
       <c r="V89" t="n">
-        <v>49.37059</v>
+        <v>49.25803</v>
       </c>
       <c r="W89" t="n">
-        <v>-107.01199</v>
+        <v>-107.09301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6078</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6730,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-1 Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101/03-10-017-14W3/00] (B A Sask Lndg Wilhelm 3 10 17 14)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4074</v>
+        <v>4313</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6783,14 +6783,14 @@
         <v>30</v>
       </c>
       <c r="V90" t="n">
-        <v>49.60125</v>
+        <v>50.41372</v>
       </c>
       <c r="W90" t="n">
-        <v>-105.74607</v>
+        <v>-107.85215</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
         </is>
       </c>
     </row>
@@ -6800,11 +6800,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/16-27-009-11W3/00]</t>
+          <t>Fusilier North Mine</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>6005</v>
+        <v>4331</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I91" t="b">
@@ -6853,14 +6853,14 @@
         <v>30</v>
       </c>
       <c r="V91" t="n">
-        <v>49.77022</v>
+        <v>51.91661</v>
       </c>
       <c r="W91" t="n">
-        <v>-107.40787</v>
+        <v>-109.79822</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
         </is>
       </c>
     </row>
@@ -6870,11 +6870,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Helium Production Well [102/10-09-006-22W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [101/10-03-005-08W3/00] (CVE Mankota 10-3-5-8)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>6004</v>
+        <v>4064</v>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I92" t="b">
@@ -6923,14 +6923,14 @@
         <v>30</v>
       </c>
       <c r="V92" t="n">
-        <v>49.46027</v>
+        <v>49.35669</v>
       </c>
       <c r="W92" t="n">
-        <v>-108.90729</v>
+        <v>-107.12482</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4064</t>
         </is>
       </c>
     </row>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/06-30-003-26W3/00]</t>
+          <t>Deadwood Formation Helium Production Well [102/10-25-003-27W3/00] (North American Helium Battle Creek 10-25-03-27W3)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6003</v>
+        <v>4060</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -6993,14 +6993,14 @@
         <v>30</v>
       </c>
       <c r="V93" t="n">
-        <v>49.23862</v>
+        <v>49.23949</v>
       </c>
       <c r="W93" t="n">
-        <v>-109.49394</v>
+        <v>-109.51141</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4060</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/09-31-003-26W3/00]</t>
+          <t>Great Lakes Ceramics Quarry</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6002</v>
+        <v>3975</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7025,12 +7025,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I94" t="b">
@@ -7063,14 +7063,14 @@
         <v>30</v>
       </c>
       <c r="V94" t="n">
-        <v>49.25465</v>
+        <v>49.20355</v>
       </c>
       <c r="W94" t="n">
-        <v>-109.48226</v>
+        <v>-106.07015</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Helium Production Well [101/11-34-009-11W3/00]</t>
+          <t>Estevan Brick 72H-1 Quarry</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6006</v>
+        <v>4074</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I95" t="b">
@@ -7133,14 +7133,14 @@
         <v>30</v>
       </c>
       <c r="V95" t="n">
-        <v>49.77601</v>
+        <v>49.60125</v>
       </c>
       <c r="W95" t="n">
-        <v>-107.428</v>
+        <v>-105.74607</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
         </is>
       </c>
     </row>
@@ -7150,11 +7150,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I-XL Quarries</t>
+          <t>Midland Mine</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4286</v>
+        <v>4073</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7203,14 +7203,14 @@
         <v>30</v>
       </c>
       <c r="V96" t="n">
-        <v>50.00928</v>
+        <v>49.4577</v>
       </c>
       <c r="W96" t="n">
-        <v>-105.15722</v>
+        <v>-105.64778</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
         </is>
       </c>
     </row>
@@ -7220,11 +7220,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-3 Quarry</t>
+          <t>Estevan Brick 72H-4 Quarry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7273,14 +7273,14 @@
         <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>49.58841</v>
+        <v>49.63087</v>
       </c>
       <c r="W97" t="n">
-        <v>-105.79049</v>
+        <v>-105.78917</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
         </is>
       </c>
     </row>
@@ -7290,11 +7290,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Wapaw Bay Lignite-Leonardite Deposits</t>
+          <t>Estevan Brick 72H-3 Quarry</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>671</v>
+        <v>4076</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Leonardite, Coal</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I98" t="b">
@@ -7334,23 +7334,23 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T98" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U98" t="n">
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>54.86112</v>
+        <v>49.58841</v>
       </c>
       <c r="W98" t="n">
-        <v>-104.66112</v>
+        <v>-105.79049</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
         </is>
       </c>
     </row>
@@ -7360,27 +7360,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Triana Iron Deposit</t>
+          <t>I-XL Quarries</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1620</v>
+        <v>4286</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Iron, Titanium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7410,17 +7410,17 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>59.23056</v>
+        <v>50.00928</v>
       </c>
       <c r="W99" t="n">
-        <v>-105.43974</v>
+        <v>-105.15722</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1620</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
         </is>
       </c>
     </row>
@@ -7430,27 +7430,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Triangle Lake Fe-Ti Showing</t>
+          <t>Dominion Firebrick Quarry</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>819</v>
+        <v>4287</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Iron, Cobalt, Copper, Nickel, Titanium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I100" t="b">
@@ -7474,21 +7474,861 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
+        <v>13</v>
+      </c>
+      <c r="T100" t="n">
+        <v>325</v>
+      </c>
+      <c r="U100" t="n">
+        <v>30</v>
+      </c>
+      <c r="V100" t="n">
+        <v>50.02441</v>
+      </c>
+      <c r="W100" t="n">
+        <v>-105.22623</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>A.P. Green Quarry</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4288</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Kaolin</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Deposit: Post-Production</t>
+        </is>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>13</v>
+      </c>
+      <c r="T101" t="n">
+        <v>325</v>
+      </c>
+      <c r="U101" t="n">
+        <v>30</v>
+      </c>
+      <c r="V101" t="n">
+        <v>50.09003</v>
+      </c>
+      <c r="W101" t="n">
+        <v>-105.43064</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [111/11-03-017-14W3/00] (Gulf Wilhelm11-3-17-14)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>4311</v>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Deposit: Post-Production</t>
+        </is>
+      </c>
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>13</v>
+      </c>
+      <c r="T102" t="n">
+        <v>325</v>
+      </c>
+      <c r="U102" t="n">
+        <v>30</v>
+      </c>
+      <c r="V102" t="n">
+        <v>50.40618</v>
+      </c>
+      <c r="W102" t="n">
+        <v>-107.85048</v>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Souris River Formation Helium Production Well [141/05-31-003-26W3/00] (Interex Battle Creek West 5-31-3-26)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>5558</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>13</v>
+      </c>
+      <c r="T103" t="n">
+        <v>325</v>
+      </c>
+      <c r="U103" t="n">
+        <v>30</v>
+      </c>
+      <c r="V103" t="n">
+        <v>49.25304</v>
+      </c>
+      <c r="W103" t="n">
+        <v>-109.50042</v>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5558</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [101/09-35-003-09W3/00] (NAH Mankota DD 2C12-36-2A9-35-3-9)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>6080</v>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>13</v>
+      </c>
+      <c r="T104" t="n">
+        <v>325</v>
+      </c>
+      <c r="U104" t="n">
+        <v>30</v>
+      </c>
+      <c r="V104" t="n">
+        <v>49.25484</v>
+      </c>
+      <c r="W104" t="n">
+        <v>-107.10681</v>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6080</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [101/09-31-003-26W3/00] (North American Helium Battle Creek 9-31-3-26)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>6002</v>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>13</v>
+      </c>
+      <c r="T105" t="n">
+        <v>325</v>
+      </c>
+      <c r="U105" t="n">
+        <v>30</v>
+      </c>
+      <c r="V105" t="n">
+        <v>49.25465</v>
+      </c>
+      <c r="W105" t="n">
+        <v>-109.48226</v>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [101/14-03-017-14W3/00] (Canadian Helium Wilhelm 14-3-17-14)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>6021</v>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>13</v>
+      </c>
+      <c r="T106" t="n">
+        <v>325</v>
+      </c>
+      <c r="U106" t="n">
+        <v>30</v>
+      </c>
+      <c r="V106" t="n">
+        <v>50.41137</v>
+      </c>
+      <c r="W106" t="n">
+        <v>-107.85382</v>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [102/01-09-017-14W3/00] (B.A. Wilhelm 1 A 9)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>5550</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Deposit: Post-Production</t>
+        </is>
+      </c>
+      <c r="I107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>13</v>
+      </c>
+      <c r="T107" t="n">
+        <v>325</v>
+      </c>
+      <c r="U107" t="n">
+        <v>30</v>
+      </c>
+      <c r="V107" t="n">
+        <v>50.41339</v>
+      </c>
+      <c r="W107" t="n">
+        <v>-107.86357</v>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [101/16-14-004-09W3/00] (NAH Mankota West DD 4A16-14-1C16-14-4-9)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>6019</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>13</v>
+      </c>
+      <c r="T108" t="n">
+        <v>325</v>
+      </c>
+      <c r="U108" t="n">
+        <v>30</v>
+      </c>
+      <c r="V108" t="n">
+        <v>49.30389</v>
+      </c>
+      <c r="W108" t="n">
+        <v>-107.10893</v>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [141/02-09-017-14W3/00] (IAC Wilhelm 2-9-17-14)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>5549</v>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I109" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>13</v>
+      </c>
+      <c r="T109" t="n">
+        <v>325</v>
+      </c>
+      <c r="U109" t="n">
+        <v>30</v>
+      </c>
+      <c r="V109" t="n">
+        <v>50.41544</v>
+      </c>
+      <c r="W109" t="n">
+        <v>-107.86935</v>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deadwood Formation Helium Production Well [101/12-25-004-09W3/00] (NAH Mankota DD 4D8-26-1B12-25-4-9)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>6020</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Helium</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Deposit: Production</t>
+        </is>
+      </c>
+      <c r="I110" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>13</v>
+      </c>
+      <c r="T110" t="n">
+        <v>325</v>
+      </c>
+      <c r="U110" t="n">
+        <v>30</v>
+      </c>
+      <c r="V110" t="n">
+        <v>49.32802</v>
+      </c>
+      <c r="W110" t="n">
+        <v>-107.10274</v>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Triana Iron Deposit</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1620</v>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Iron, Titanium</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Deposit: Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I111" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>13</v>
+      </c>
+      <c r="T111" t="n">
+        <v>325</v>
+      </c>
+      <c r="U111" t="n">
+        <v>29</v>
+      </c>
+      <c r="V111" t="n">
+        <v>59.23056</v>
+      </c>
+      <c r="W111" t="n">
+        <v>-105.43974</v>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1620</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Triangle Lake Fe-Ti Showing</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>819</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Iron, Cobalt, Copper, Nickel, Titanium</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Deposit: Advanced Exploration</t>
+        </is>
+      </c>
+      <c r="I112" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
         <v>11</v>
       </c>
-      <c r="T100" t="n">
+      <c r="T112" t="n">
         <v>275</v>
       </c>
-      <c r="U100" t="n">
+      <c r="U112" t="n">
         <v>29</v>
       </c>
-      <c r="V100" t="n">
+      <c r="V112" t="n">
         <v>55.5764</v>
       </c>
-      <c r="W100" t="n">
+      <c r="W112" t="n">
         <v>-104.97695</v>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0819</t>
         </is>

--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -570,22 +570,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
+          <t>Fond Du Lac Uranium Deposit</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5996</v>
+        <v>1572</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Uranium, Iron</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -623,14 +623,14 @@
         <v>38</v>
       </c>
       <c r="V2" t="n">
-        <v>49.56951</v>
+        <v>59.30417</v>
       </c>
       <c r="W2" t="n">
-        <v>-103.14392</v>
+        <v>-107.16668</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
         </is>
       </c>
     </row>
@@ -710,11 +710,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [04-15-032-23W3]</t>
+          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6076</v>
+        <v>5996</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -763,14 +763,14 @@
         <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>51.73895</v>
+        <v>49.56951</v>
       </c>
       <c r="W4" t="n">
-        <v>-109.19123</v>
+        <v>-103.14392</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deep Bay Graphite Deposit</t>
+          <t>Duperow Formation Lithium Exploration Well [04-15-032-23W3]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>480</v>
+        <v>6076</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -833,14 +833,14 @@
         <v>38</v>
       </c>
       <c r="V5" t="n">
-        <v>56.38334</v>
+        <v>51.73895</v>
       </c>
       <c r="W5" t="n">
-        <v>-103.12501</v>
+        <v>-109.19123</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6076</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fond Du Lac Uranium Deposit</t>
+          <t>Deep Bay Graphite Deposit</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1572</v>
+        <v>480</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Uranium, Iron</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -903,14 +903,14 @@
         <v>38</v>
       </c>
       <c r="V6" t="n">
-        <v>59.30417</v>
+        <v>56.38334</v>
       </c>
       <c r="W6" t="n">
-        <v>-107.16668</v>
+        <v>-103.12501</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
         </is>
       </c>
     </row>
@@ -920,11 +920,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gollier Creek Mine</t>
+          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2780</v>
+        <v>5547</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Deposit: Development</t>
+          <t>Deposit: Advanced Exploration</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -973,14 +973,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>49.41374</v>
+        <v>49.01463</v>
       </c>
       <c r="W7" t="n">
-        <v>-106.24081</v>
+        <v>-109.73056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
         </is>
       </c>
     </row>
@@ -990,11 +990,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bitter Lake Deposit</t>
+          <t>Basin Lake</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3673</v>
+        <v>5043</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,14 +1043,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>50.10616</v>
+        <v>52.60621</v>
       </c>
       <c r="W8" t="n">
-        <v>-109.79816</v>
+        <v>-105.2732</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lydden Lake Deposit</t>
+          <t>Redberry Lake</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3676</v>
+        <v>5044</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1113,14 +1113,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>52.01647</v>
+        <v>52.69009</v>
       </c>
       <c r="W9" t="n">
-        <v>-108.36644</v>
+        <v>-107.16763</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
         </is>
       </c>
     </row>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 1</t>
+          <t>Eins Lake</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3849</v>
+        <v>4369</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1183,14 +1183,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>49.52546</v>
+        <v>52.04888</v>
       </c>
       <c r="W10" t="n">
-        <v>-108.84275</v>
+        <v>-108.51676</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 2</t>
+          <t>BA Wilhelm 1-9</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3861</v>
+        <v>4312</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1253,14 +1253,14 @@
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>49.50293</v>
+        <v>50.41172</v>
       </c>
       <c r="W11" t="n">
-        <v>-109.01845</v>
+        <v>-107.86309</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wood Mountain Ridge Resource Area</t>
+          <t>Talisman Bures 11-17-9-21</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3972</v>
+        <v>5548</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1323,14 +1323,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>49.41751</v>
+        <v>49.73459</v>
       </c>
       <c r="W12" t="n">
-        <v>-106.3298</v>
+        <v>-104.81905</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Waverly Ridge Resource Area</t>
+          <t>DEML et al Bigstick 6-14-13-26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3973</v>
+        <v>5551</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1393,14 +1393,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>49.36742</v>
+        <v>50.08028</v>
       </c>
       <c r="W13" t="n">
-        <v>-106.49029</v>
+        <v>-109.45467</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ingebrigt North Deposit</t>
+          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3669</v>
+        <v>5552</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1463,14 +1463,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>50.40828</v>
+        <v>49.34918</v>
       </c>
       <c r="W14" t="n">
-        <v>-109.38439</v>
+        <v>-104.82203</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aroma Lake Deposit</t>
+          <t>Canera Francis 6-36-12-15</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3668</v>
+        <v>5553</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,14 +1533,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>52.29156</v>
+        <v>50.03521</v>
       </c>
       <c r="W15" t="n">
-        <v>-108.55453</v>
+        <v>-103.9312</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
         </is>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rockglen</t>
+          <t>Lydden Lake Deposit</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3976</v>
+        <v>3676</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bentonite, Volcanic Ash</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1603,14 +1603,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>49.19705</v>
+        <v>52.01647</v>
       </c>
       <c r="W16" t="n">
-        <v>-106.03823</v>
+        <v>-108.36644</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-2</t>
+          <t>Wood Mountain Ridge Resource Area</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4075</v>
+        <v>3972</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1673,14 +1673,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>49.57279</v>
+        <v>49.41751</v>
       </c>
       <c r="W17" t="n">
-        <v>-105.74453</v>
+        <v>-106.3298</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-5</t>
+          <t>Eastend Resource Area</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4078</v>
+        <v>3866</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1743,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="V18" t="n">
-        <v>49.63023</v>
+        <v>49.40637</v>
       </c>
       <c r="W18" t="n">
-        <v>-105.81014</v>
+        <v>-108.62578</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
         </is>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-6</t>
+          <t>Estevan Brick Kaolin 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4079</v>
+        <v>3861</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1813,14 +1813,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>49.61548</v>
+        <v>49.50293</v>
       </c>
       <c r="W19" t="n">
-        <v>-105.81093</v>
+        <v>-109.01845</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1830,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eins Lake</t>
+          <t>Rockglen</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4369</v>
+        <v>3976</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Bentonite, Volcanic Ash</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1883,14 +1883,14 @@
         <v>35</v>
       </c>
       <c r="V20" t="n">
-        <v>52.04888</v>
+        <v>49.19705</v>
       </c>
       <c r="W20" t="n">
-        <v>-108.51676</v>
+        <v>-106.03823</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
         </is>
       </c>
     </row>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1-9</t>
+          <t>Waverly Ridge Resource Area</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4312</v>
+        <v>3973</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1953,14 +1953,14 @@
         <v>35</v>
       </c>
       <c r="V21" t="n">
-        <v>50.41172</v>
+        <v>49.36742</v>
       </c>
       <c r="W21" t="n">
-        <v>-107.86309</v>
+        <v>-106.49029</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
         </is>
       </c>
     </row>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
+          <t>Estevan Brick 72H-6</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5552</v>
+        <v>4079</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2023,14 +2023,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>49.34918</v>
+        <v>49.61548</v>
       </c>
       <c r="W22" t="n">
-        <v>-104.82203</v>
+        <v>-105.81093</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Canera Francis 6-36-12-15</t>
+          <t>Estevan Brick 72H-5</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5553</v>
+        <v>4078</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2093,14 +2093,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>50.03521</v>
+        <v>49.63023</v>
       </c>
       <c r="W23" t="n">
-        <v>-103.9312</v>
+        <v>-105.81014</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
         </is>
       </c>
     </row>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEML et al Bigstick 6-14-13-26</t>
+          <t>Estevan Brick 72H-2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5551</v>
+        <v>4075</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,14 +2163,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>50.08028</v>
+        <v>49.57279</v>
       </c>
       <c r="W24" t="n">
-        <v>-109.45467</v>
+        <v>-105.74453</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
         </is>
       </c>
     </row>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
+          <t>Axe Lake Deposit</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5547</v>
+        <v>2784</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Oil Sand</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2233,14 +2233,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>49.01463</v>
+        <v>57.20387</v>
       </c>
       <c r="W25" t="n">
-        <v>-109.73056</v>
+        <v>-109.9058</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
         </is>
       </c>
     </row>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Talisman Bures 11-17-9-21</t>
+          <t>Gollier Creek Mine</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5548</v>
+        <v>2780</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Development</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2303,14 +2303,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>49.73459</v>
+        <v>49.41374</v>
       </c>
       <c r="W26" t="n">
-        <v>-104.81905</v>
+        <v>-106.24081</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Redberry Lake</t>
+          <t>Sybouts West Deposit</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5044</v>
+        <v>3672</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2373,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>52.69009</v>
+        <v>49.04192</v>
       </c>
       <c r="W27" t="n">
-        <v>-107.16763</v>
+        <v>-104.53479</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
         </is>
       </c>
     </row>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Basin Lake</t>
+          <t>Bitter Lake Deposit</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5043</v>
+        <v>3673</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2443,14 +2443,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>52.60621</v>
+        <v>50.10616</v>
       </c>
       <c r="W28" t="n">
-        <v>-105.2732</v>
+        <v>-109.79816</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Eastend Resource Area</t>
+          <t>Aroma Lake Deposit</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3866</v>
+        <v>3668</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2513,14 +2513,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>49.40637</v>
+        <v>52.29156</v>
       </c>
       <c r="W29" t="n">
-        <v>-108.62578</v>
+        <v>-108.55453</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Verlo East Deposit</t>
+          <t>Estevan Brick Kaolin 1</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3671</v>
+        <v>3849</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2583,14 +2583,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>50.33614</v>
+        <v>49.52546</v>
       </c>
       <c r="W30" t="n">
-        <v>-108.45696</v>
+        <v>-108.84275</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sybouts West Deposit</t>
+          <t>Ingebrigt North Deposit</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3672</v>
+        <v>3669</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>49.04192</v>
+        <v>50.40828</v>
       </c>
       <c r="W31" t="n">
-        <v>-104.53479</v>
+        <v>-109.38439</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C28 Kimberlite</t>
+          <t>Verlo East Deposit</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2864</v>
+        <v>3671</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2723,14 +2723,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>53.70316</v>
+        <v>50.33614</v>
       </c>
       <c r="W32" t="n">
-        <v>-104.85739</v>
+        <v>-108.45696</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Axe Lake Deposit</t>
+          <t>C28 Kimberlite</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2784</v>
+        <v>2864</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oil Sand</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2793,14 +2793,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>57.20387</v>
+        <v>53.70316</v>
       </c>
       <c r="W33" t="n">
-        <v>-109.9058</v>
+        <v>-104.85739</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2810,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/15-09-005-21W3/02] (North American Helium Whitemud 15-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-36-003-27W3/00] (NAH Battle Creek DD 3C6-36-3B6-36-3-27W3)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6087</v>
+        <v>6081</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2863,14 +2863,14 @@
         <v>30</v>
       </c>
       <c r="V34" t="n">
-        <v>49.3769</v>
+        <v>49.252</v>
       </c>
       <c r="W34" t="n">
-        <v>-108.76953</v>
+        <v>-109.51999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6087</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6081</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Truax Quarry</t>
+          <t>Deadwood Formation Helium Production Well [102/15-35-009-11W3/00] (North American Helium Ponteix 15-35-9-11)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2782</v>
+        <v>6010</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bentonite</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -2933,14 +2933,14 @@
         <v>30</v>
       </c>
       <c r="V35" t="n">
-        <v>49.96019</v>
+        <v>49.78513</v>
       </c>
       <c r="W35" t="n">
-        <v>-104.81877</v>
+        <v>-107.39009</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-09-006-22W3/00] (NAH Eastend 14-9-6-22)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-30-003-26W3/00] (North American Helium Battle Creek W 6-3)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6085</v>
+        <v>6003</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3003,14 +3003,14 @@
         <v>30</v>
       </c>
       <c r="V36" t="n">
-        <v>49.46254</v>
+        <v>49.23862</v>
       </c>
       <c r="W36" t="n">
-        <v>-108.90993</v>
+        <v>-109.49394</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6085</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
         </is>
       </c>
     </row>
@@ -3020,11 +3020,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-07-016-16W3/00] (NAH Antelope Lake DD 2C14-7-1B14-7-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/09-31-003-26W3/00] (North American Helium Battle Creek 9-31-3-26)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6082</v>
+        <v>6002</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3073,14 +3073,14 @@
         <v>30</v>
       </c>
       <c r="V37" t="n">
-        <v>50.33577</v>
+        <v>49.25465</v>
       </c>
       <c r="W37" t="n">
-        <v>-108.19537</v>
+        <v>-109.48226</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6082</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/02-18-016-16W3/00] (NAH Antelope Lake DD 1C2-18-3D2-18-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-28-009-11W3/00] (NAH Cadillac DD 1D16-28-1D16-28-9-11)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6084</v>
+        <v>6008</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3143,14 +3143,14 @@
         <v>30</v>
       </c>
       <c r="V38" t="n">
-        <v>50.34284</v>
+        <v>49.76938</v>
       </c>
       <c r="W38" t="n">
-        <v>-108.18985</v>
+        <v>-107.42801</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6084</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/02-17-016-16W3/00] (NAH Antelope Lake DD 4A2-17-4D2-17-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-35-009-11W3/00] (NAH Cadillac DD 2A11-35-3D6-35-9-11)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6083</v>
+        <v>6009</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3213,14 +3213,14 @@
         <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>50.342</v>
+        <v>49.77879</v>
       </c>
       <c r="W39" t="n">
-        <v>-108.16593</v>
+        <v>-107.39509</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6083</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [121/07-09-017-14W3/00] (Gulf Sask Landing Wilhelm 7 9 17 14)</t>
+          <t>Deadwood Formation Helium Production Well [101/11-34-009-11W3/00] (NAH Cadillac DD 4A8-33-3B11-34-9-11)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6088</v>
+        <v>6006</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3283,14 +3283,14 @@
         <v>30</v>
       </c>
       <c r="V40" t="n">
-        <v>50.41642</v>
+        <v>49.77938</v>
       </c>
       <c r="W40" t="n">
-        <v>-107.87088</v>
+        <v>-107.42112</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6088</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [101/11-34-002-26W3/04] (NAH Battle Creek DD 1C11-34-2B14-34-2-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-27-009-11W3/00] (NAH Cadillac 16-27-9-11W3)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6086</v>
+        <v>6005</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3353,14 +3353,14 @@
         <v>30</v>
       </c>
       <c r="V41" t="n">
-        <v>49.17016</v>
+        <v>49.77022</v>
       </c>
       <c r="W41" t="n">
-        <v>-109.40476</v>
+        <v>-107.40787</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6086</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wapaw Bay Mine</t>
+          <t>Souris River Formation Helium Production Well [102/10-09-006-22W3/00] (North American Helium Eastend 10B-9-6-22)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>671</v>
+        <v>6004</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leonardite, Coal (Non-Metallurgical)</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3414,23 +3414,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>30</v>
       </c>
       <c r="V42" t="n">
-        <v>54.86112</v>
+        <v>49.46027</v>
       </c>
       <c r="W42" t="n">
-        <v>-104.66112</v>
+        <v>-108.90729</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3440,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Willow Bunch Clinker Shale Mine</t>
+          <t>Deadwood Formation Helium Production Well [101/01-03-010-11W3/00] (NAH Cadillac DD 3C4-2-1C1-3-10-11)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2781</v>
+        <v>6007</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Clinker</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3493,14 +3493,14 @@
         <v>30</v>
       </c>
       <c r="V43" t="n">
-        <v>49.32932</v>
+        <v>49.78761</v>
       </c>
       <c r="W43" t="n">
-        <v>-105.52988</v>
+        <v>-107.40843</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
         </is>
       </c>
     </row>
@@ -3510,11 +3510,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [102/03-35-005-27W3/04] (NAH Consul DD 1C2-35-2C2-35-5-27)</t>
+          <t>Deadwood Formation Helium Production Well [101-10-01-004-09W3/00] (NAH Mankota DD 3C9-1-2A10-1-4-9)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6012</v>
+        <v>6079</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3563,14 +3563,14 @@
         <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>49.42389</v>
+        <v>49.26926</v>
       </c>
       <c r="W44" t="n">
-        <v>-109.53802</v>
+        <v>-107.09053</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6079</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/16-21-005-27W3/02] (NAH Consul 16A-21-5-27)</t>
+          <t>Deadwood Formation Helium Production Well [101/09-35-003-09W3/00] (NAH Mankota DD 2C12-36-2A9-35-3-9)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6013</v>
+        <v>6080</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3633,14 +3633,14 @@
         <v>30</v>
       </c>
       <c r="V45" t="n">
-        <v>49.40655</v>
+        <v>49.25484</v>
       </c>
       <c r="W45" t="n">
-        <v>-109.5718</v>
+        <v>-107.10681</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6080</t>
         </is>
       </c>
     </row>
@@ -3650,11 +3650,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [103/08-04-006-26W3/02] (NAH Cypress 4C8-4-6-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-03-017-14W3/00] (Canadian Helium Wilhelm 14-3-17-14)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6014</v>
+        <v>6021</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3703,14 +3703,14 @@
         <v>30</v>
       </c>
       <c r="V46" t="n">
-        <v>49.44309</v>
+        <v>50.41137</v>
       </c>
       <c r="W46" t="n">
-        <v>-109.44006</v>
+        <v>-107.85382</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/16-27-005-26W3/00] (NAH Cypress DD 1B1-34-4C16-27-5-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/10-36-003-09W3/02] (NAH Mankota DD 1C14-36-3C10-36-3-9)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6015</v>
+        <v>6078</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3773,14 +3773,14 @@
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>49.42103</v>
+        <v>49.25803</v>
       </c>
       <c r="W47" t="n">
-        <v>-109.41718</v>
+        <v>-107.09301</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6078</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/14-34-005-26W3/00] (NAH Cypress 14-34-5-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/12-25-004-09W3/00] (NAH Mankota DD 4D8-26-1B12-25-4-9)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6016</v>
+        <v>6020</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>49.43366</v>
+        <v>49.32802</v>
       </c>
       <c r="W48" t="n">
-        <v>-109.4287</v>
+        <v>-107.10274</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
         </is>
       </c>
     </row>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/05-26-004-09W3/00] (NAH Mankota DD 2D5-26-4C5-26-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-14-004-09W3/00] (NAH Mankota West DD 4A16-14-1C16-14-4-9)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6017</v>
+        <v>6019</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3913,14 +3913,14 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>49.32636</v>
+        <v>49.30389</v>
       </c>
       <c r="W49" t="n">
-        <v>-107.12461</v>
+        <v>-107.10893</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-15-004-09W3/00] (NAH Mankota West DD 1D16-15-2D16-15-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/05-26-004-09W3/00] (NAH Mankota DD 2D5-26-4C5-26-4-9)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6018</v>
+        <v>6017</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -3983,14 +3983,14 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>49.3046</v>
+        <v>49.32636</v>
       </c>
       <c r="W50" t="n">
-        <v>-107.12846</v>
+        <v>-107.12461</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [102/10-09-006-22W3/00] (North American Helium Eastend 10B-9-6-22)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-15-004-09W3/00] (NAH Mankota West DD 1D16-15-2D16-15-4-9)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6004</v>
+        <v>6018</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4053,14 +4053,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>49.46027</v>
+        <v>49.3046</v>
       </c>
       <c r="W51" t="n">
-        <v>-108.90729</v>
+        <v>-107.12846</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-27-009-11W3/00] (NAH Cadillac 16-27-9-11W3)</t>
+          <t>Deadwood Formation Helium Production Well [103/08-04-006-26W3/02] (NAH Cypress 4C8-4-6-26)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6005</v>
+        <v>6014</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4123,14 +4123,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>49.77022</v>
+        <v>49.44309</v>
       </c>
       <c r="W52" t="n">
-        <v>-107.40787</v>
+        <v>-109.44006</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/11-34-009-11W3/00] (NAH Cadillac DD 4A8-33-3B11-34-9-11)</t>
+          <t>Souris River Formation Helium Production Well [101/16-21-005-27W3/02] (NAH Consul 16A-21-5-27)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6006</v>
+        <v>6013</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4193,14 +4193,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>49.77938</v>
+        <v>49.40655</v>
       </c>
       <c r="W53" t="n">
-        <v>-107.42112</v>
+        <v>-109.5718</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/01-03-010-11W3/00] (NAH Cadillac DD 3C4-2-1C1-3-10-11)</t>
+          <t>Deadwood Formation Helium Production Well [102/14-34-005-26W3/00] (NAH Cypress 14-34-5-26)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6007</v>
+        <v>6016</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4263,14 +4263,14 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>49.78761</v>
+        <v>49.43366</v>
       </c>
       <c r="W54" t="n">
-        <v>-107.40843</v>
+        <v>-109.4287</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
         </is>
       </c>
     </row>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-28-009-11W3/00] (NAH Cadillac DD 1D16-28-1D16-28-9-11)</t>
+          <t>Souris River Formation Helium Production Well [101/16-27-005-26W3/00] (NAH Cypress DD 1B1-34-4C16-27-5-26)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6008</v>
+        <v>6015</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4333,14 +4333,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>49.76938</v>
+        <v>49.42103</v>
       </c>
       <c r="W55" t="n">
-        <v>-107.42801</v>
+        <v>-109.41718</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-35-009-11W3/00] (NAH Cadillac DD 2A11-35-3D6-35-9-11)</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [102/03-35-005-27W3/04] (NAH Consul DD 1C2-35-2C2-35-5-27)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6009</v>
+        <v>6012</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4403,14 +4403,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>49.77879</v>
+        <v>49.42389</v>
       </c>
       <c r="W56" t="n">
-        <v>-107.39509</v>
+        <v>-109.53802</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
         </is>
       </c>
     </row>
@@ -4420,11 +4420,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/15-35-009-11W3/00] (North American Helium Ponteix 15-35-9-11)</t>
+          <t>Truax Quarry</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6010</v>
+        <v>2782</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4473,14 +4473,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>49.78513</v>
+        <v>49.96019</v>
       </c>
       <c r="W57" t="n">
-        <v>-107.39009</v>
+        <v>-104.81877</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-36-003-27W3/00] (NAH Battle Creek DD 3C6-36-3B6-36-3-27W3)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-09-006-22W3/00] (NAH Eastend 14-9-6-22)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6081</v>
+        <v>6085</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4613,14 +4613,14 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>49.252</v>
+        <v>49.46254</v>
       </c>
       <c r="W59" t="n">
-        <v>-109.51999</v>
+        <v>-108.90993</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6081</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6085</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101-10-01-004-09W3/00] (NAH Mankota DD 3C9-1-2A10-1-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/03-10-017-14W3/00] (B A Sask Lndg Wilhelm 3 10 17 14)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6079</v>
+        <v>4313</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -4683,14 +4683,14 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>49.26926</v>
+        <v>50.41372</v>
       </c>
       <c r="W60" t="n">
-        <v>-107.09053</v>
+        <v>-107.85215</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6079</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/12-10-005-08W3/00] (CVE Mankota 12-10-5-8)</t>
+          <t>Estevan Brick 72G Quarry</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4063</v>
+        <v>3974</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4823,14 +4823,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>49.37259</v>
+        <v>49.20739</v>
       </c>
       <c r="W62" t="n">
-        <v>-107.01264</v>
+        <v>-106.06351</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
         </is>
       </c>
     </row>
@@ -4910,11 +4910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 3</t>
+          <t>Ravenscrag Quarry</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3863</v>
+        <v>3865</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -4963,14 +4963,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>49.51582</v>
+        <v>49.49081</v>
       </c>
       <c r="W64" t="n">
-        <v>-109.01757</v>
+        <v>-109.14115</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Estevan Brick 72G Quarry</t>
+          <t>Plainsman Quarry 3</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3974</v>
+        <v>3863</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5103,14 +5103,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>49.20739</v>
+        <v>49.51582</v>
       </c>
       <c r="W66" t="n">
-        <v>-106.06351</v>
+        <v>-109.01757</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Knolly Quarry</t>
+          <t>Day Quarry</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3855</v>
+        <v>3857</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5173,14 +5173,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>49.46895</v>
+        <v>49.51123</v>
       </c>
       <c r="W67" t="n">
-        <v>-108.92433</v>
+        <v>-108.84032</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
         </is>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>I-XL Industries 1 Quarry</t>
+          <t>Knolly Quarry</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3853</v>
+        <v>3855</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5313,14 +5313,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>49.46928</v>
+        <v>49.46895</v>
       </c>
       <c r="W69" t="n">
-        <v>-108.83703</v>
+        <v>-108.92433</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
         </is>
       </c>
     </row>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Day Quarry</t>
+          <t>I-XL Industries 1 Quarry</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3857</v>
+        <v>3853</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5383,14 +5383,14 @@
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>49.51123</v>
+        <v>49.46928</v>
       </c>
       <c r="W70" t="n">
-        <v>-108.84032</v>
+        <v>-108.83703</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Old Pit Quarry</t>
+          <t>Plainsman Quarry 1</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3858</v>
+        <v>3860</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5523,14 +5523,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>49.47594</v>
+        <v>49.49048</v>
       </c>
       <c r="W72" t="n">
-        <v>-109.01306</v>
+        <v>-109.04754</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ravenscrag Quarry</t>
+          <t>Old Pit Quarry</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3865</v>
+        <v>3858</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5663,14 +5663,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>49.49081</v>
+        <v>49.47594</v>
       </c>
       <c r="W74" t="n">
-        <v>-109.14115</v>
+        <v>-109.01306</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
         </is>
       </c>
     </row>
@@ -5680,11 +5680,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ceylon Lake Deposit</t>
+          <t>Estevan Brick Location 2</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3670</v>
+        <v>3690</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5733,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>49.28985</v>
+        <v>49.12208</v>
       </c>
       <c r="W75" t="n">
-        <v>-104.70435</v>
+        <v>-103.07029</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
         </is>
       </c>
     </row>
@@ -5820,11 +5820,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 2</t>
+          <t>Dempster Clay Pit</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3690</v>
+        <v>3851</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -5873,14 +5873,14 @@
         <v>30</v>
       </c>
       <c r="V77" t="n">
-        <v>49.12208</v>
+        <v>49.52823</v>
       </c>
       <c r="W77" t="n">
-        <v>-103.07029</v>
+        <v>-108.84206</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dempster Clay Pit</t>
+          <t>Estevan Brick Location 1</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3851</v>
+        <v>3689</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -5943,14 +5943,14 @@
         <v>30</v>
       </c>
       <c r="V78" t="n">
-        <v>49.52823</v>
+        <v>49.06449</v>
       </c>
       <c r="W78" t="n">
-        <v>-108.84206</v>
+        <v>-103.06979</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
         </is>
       </c>
     </row>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 1</t>
+          <t>Ceylon Lake Deposit</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3689</v>
+        <v>3670</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>30</v>
       </c>
       <c r="V79" t="n">
-        <v>49.06449</v>
+        <v>49.28985</v>
       </c>
       <c r="W79" t="n">
-        <v>-103.06979</v>
+        <v>-104.70435</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frederick Lake Mine</t>
+          <t>Snakehole Lake Mine</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3664</v>
+        <v>3666</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6083,14 +6083,14 @@
         <v>30</v>
       </c>
       <c r="V80" t="n">
-        <v>50.00971</v>
+        <v>50.50916</v>
       </c>
       <c r="W80" t="n">
-        <v>-105.77947</v>
+        <v>-108.47667</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chaplin Mine</t>
+          <t>Frederick Lake Mine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3657</v>
+        <v>3664</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6153,14 +6153,14 @@
         <v>30</v>
       </c>
       <c r="V81" t="n">
-        <v>50.46073</v>
+        <v>50.00971</v>
       </c>
       <c r="W81" t="n">
-        <v>-106.66983</v>
+        <v>-105.77947</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alsask Lake Mine</t>
+          <t>Sybouts East Mine</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3661</v>
+        <v>3662</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6223,14 +6223,14 @@
         <v>30</v>
       </c>
       <c r="V82" t="n">
-        <v>51.33929</v>
+        <v>49.03697</v>
       </c>
       <c r="W82" t="n">
-        <v>-109.86516</v>
+        <v>-104.43359</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
         </is>
       </c>
     </row>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ingebrigt South Mine</t>
+          <t>Alsask Lake Mine</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3660</v>
+        <v>3661</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6293,14 +6293,14 @@
         <v>30</v>
       </c>
       <c r="V83" t="n">
-        <v>50.35665</v>
+        <v>51.33929</v>
       </c>
       <c r="W83" t="n">
-        <v>-109.32196</v>
+        <v>-109.86516</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Horseshoe Lake Mine</t>
+          <t>Ingebrigt South Mine</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6363,14 +6363,14 @@
         <v>30</v>
       </c>
       <c r="V84" t="n">
-        <v>49.71947</v>
+        <v>50.35665</v>
       </c>
       <c r="W84" t="n">
-        <v>-105.35516</v>
+        <v>-109.32196</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
         </is>
       </c>
     </row>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sybouts East Mine</t>
+          <t>Horseshoe Lake Mine</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3662</v>
+        <v>3659</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6433,14 +6433,14 @@
         <v>30</v>
       </c>
       <c r="V85" t="n">
-        <v>49.03697</v>
+        <v>49.71947</v>
       </c>
       <c r="W85" t="n">
-        <v>-104.43359</v>
+        <v>-105.35516</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6450,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Snakehole Lake Mine</t>
+          <t>Chaplin Mine</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3666</v>
+        <v>3657</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6503,14 +6503,14 @@
         <v>30</v>
       </c>
       <c r="V86" t="n">
-        <v>50.50916</v>
+        <v>50.46073</v>
       </c>
       <c r="W86" t="n">
-        <v>-108.47667</v>
+        <v>-106.66983</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
         </is>
       </c>
     </row>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 1</t>
+          <t>Willow Bunch Clinker Shale Mine</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3860</v>
+        <v>2781</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Clinker</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6573,14 +6573,14 @@
         <v>30</v>
       </c>
       <c r="V87" t="n">
-        <v>49.49048</v>
+        <v>49.32932</v>
       </c>
       <c r="W87" t="n">
-        <v>-109.04754</v>
+        <v>-105.52988</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-30-003-26W3/00] (North American Helium Battle Creek W 6-3)</t>
+          <t>Souris River Formation Helium Production Well [101/15-09-005-21W3/02] (North American Helium Whitemud 15-9)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6003</v>
+        <v>6087</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6643,14 +6643,14 @@
         <v>30</v>
       </c>
       <c r="V88" t="n">
-        <v>49.23862</v>
+        <v>49.3769</v>
       </c>
       <c r="W88" t="n">
-        <v>-109.49394</v>
+        <v>-108.76953</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6087</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/10-36-003-09W3/02] (NAH Mankota DD 1C14-36-3C10-36-3-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-07-016-16W3/00] (NAH Antelope Lake DD 2C14-7-1B14-7-16-16)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6078</v>
+        <v>6082</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>30</v>
       </c>
       <c r="V89" t="n">
-        <v>49.25803</v>
+        <v>50.33577</v>
       </c>
       <c r="W89" t="n">
-        <v>-107.09301</v>
+        <v>-108.19537</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6082</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6730,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/03-10-017-14W3/00] (B A Sask Lndg Wilhelm 3 10 17 14)</t>
+          <t>Deadwood Formation Helium Production Well [101/02-17-016-16W3/00] (NAH Antelope Lake DD 4A2-17-4D2-17-16-16)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4313</v>
+        <v>6083</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -6783,14 +6783,14 @@
         <v>30</v>
       </c>
       <c r="V90" t="n">
-        <v>50.41372</v>
+        <v>50.342</v>
       </c>
       <c r="W90" t="n">
-        <v>-107.85215</v>
+        <v>-108.16593</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6083</t>
         </is>
       </c>
     </row>
@@ -6800,11 +6800,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fusilier North Mine</t>
+          <t>Estevan Brick 72H-1 Quarry</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4331</v>
+        <v>4074</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6853,14 +6853,14 @@
         <v>30</v>
       </c>
       <c r="V91" t="n">
-        <v>51.91661</v>
+        <v>49.60125</v>
       </c>
       <c r="W91" t="n">
-        <v>-109.79822</v>
+        <v>-105.74607</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
         </is>
       </c>
     </row>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/10-25-003-27W3/00] (North American Helium Battle Creek 10-25-03-27W3)</t>
+          <t>Great Lakes Ceramics Quarry</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4060</v>
+        <v>3975</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -6993,14 +6993,14 @@
         <v>30</v>
       </c>
       <c r="V93" t="n">
-        <v>49.23949</v>
+        <v>49.20355</v>
       </c>
       <c r="W93" t="n">
-        <v>-109.51141</v>
+        <v>-106.07015</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4060</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Great Lakes Ceramics Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101/12-10-005-08W3/00] (CVE Mankota 12-10-5-8)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3975</v>
+        <v>4063</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7063,14 +7063,14 @@
         <v>30</v>
       </c>
       <c r="V94" t="n">
-        <v>49.20355</v>
+        <v>49.37259</v>
       </c>
       <c r="W94" t="n">
-        <v>-106.07015</v>
+        <v>-107.01264</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-1 Quarry</t>
+          <t>Midland Mine</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7133,14 +7133,14 @@
         <v>30</v>
       </c>
       <c r="V95" t="n">
-        <v>49.60125</v>
+        <v>49.4577</v>
       </c>
       <c r="W95" t="n">
-        <v>-105.74607</v>
+        <v>-105.64778</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
         </is>
       </c>
     </row>
@@ -7150,11 +7150,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Midland Mine</t>
+          <t>Estevan Brick 72H-4 Quarry</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4073</v>
+        <v>4077</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7203,14 +7203,14 @@
         <v>30</v>
       </c>
       <c r="V96" t="n">
-        <v>49.4577</v>
+        <v>49.63087</v>
       </c>
       <c r="W96" t="n">
-        <v>-105.64778</v>
+        <v>-105.78917</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
         </is>
       </c>
     </row>
@@ -7220,11 +7220,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-4 Quarry</t>
+          <t>Estevan Brick 72H-3 Quarry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7273,14 +7273,14 @@
         <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>49.63087</v>
+        <v>49.58841</v>
       </c>
       <c r="W97" t="n">
-        <v>-105.78917</v>
+        <v>-105.79049</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
         </is>
       </c>
     </row>
@@ -7290,11 +7290,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-3 Quarry</t>
+          <t>Dominion Firebrick Quarry</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4076</v>
+        <v>4287</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7343,14 +7343,14 @@
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>49.58841</v>
+        <v>50.02441</v>
       </c>
       <c r="W98" t="n">
-        <v>-105.79049</v>
+        <v>-105.22623</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
         </is>
       </c>
     </row>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>I-XL Quarries</t>
+          <t>Deadwood Formation Helium Production Well [102/10-25-003-27W3/00] (North American Helium Battle Creek 10-25-03-27W3)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4286</v>
+        <v>4060</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7413,14 +7413,14 @@
         <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>50.00928</v>
+        <v>49.23949</v>
       </c>
       <c r="W99" t="n">
-        <v>-105.15722</v>
+        <v>-109.51141</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4060</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7430,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dominion Firebrick Quarry</t>
+          <t>I-XL Quarries</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4287</v>
+        <v>4286</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7483,14 +7483,14 @@
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>50.02441</v>
+        <v>50.00928</v>
       </c>
       <c r="W100" t="n">
-        <v>-105.22623</v>
+        <v>-105.15722</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
         </is>
       </c>
     </row>
@@ -7500,11 +7500,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A.P. Green Quarry</t>
+          <t>Wapaw Bay Mine</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4288</v>
+        <v>671</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Leonardite, Coal (Non-Metallurgical)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I101" t="b">
@@ -7544,23 +7544,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>50.09003</v>
+        <v>54.86112</v>
       </c>
       <c r="W101" t="n">
-        <v>-105.43064</v>
+        <v>-104.66112</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
         </is>
       </c>
     </row>
@@ -7570,11 +7570,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [111/11-03-017-14W3/00] (Gulf Wilhelm11-3-17-14)</t>
+          <t>A.P. Green Quarry</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4311</v>
+        <v>4288</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7623,14 +7623,14 @@
         <v>30</v>
       </c>
       <c r="V102" t="n">
-        <v>50.40618</v>
+        <v>50.09003</v>
       </c>
       <c r="W102" t="n">
-        <v>-107.85048</v>
+        <v>-105.43064</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
         </is>
       </c>
     </row>
@@ -7640,11 +7640,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [141/05-31-003-26W3/00] (Interex Battle Creek West 5-31-3-26)</t>
+          <t>Deadwood Formation Helium Production Well [111/11-03-017-14W3/00] (Gulf Wilhelm11-3-17-14)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5558</v>
+        <v>4311</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I103" t="b">
@@ -7693,14 +7693,14 @@
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>49.25304</v>
+        <v>50.40618</v>
       </c>
       <c r="W103" t="n">
-        <v>-109.50042</v>
+        <v>-107.85048</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5558</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
         </is>
       </c>
     </row>
@@ -7710,11 +7710,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/09-35-003-09W3/00] (NAH Mankota DD 2C12-36-2A9-35-3-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/02-18-016-16W3/00] (NAH Antelope Lake DD 1C2-18-3D2-18-16-16)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6080</v>
+        <v>6084</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
@@ -7763,14 +7763,14 @@
         <v>30</v>
       </c>
       <c r="V104" t="n">
-        <v>49.25484</v>
+        <v>50.34284</v>
       </c>
       <c r="W104" t="n">
-        <v>-107.10681</v>
+        <v>-108.18985</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6080</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6084</t>
         </is>
       </c>
     </row>
@@ -7780,11 +7780,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/09-31-003-26W3/00] (North American Helium Battle Creek 9-31-3-26)</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [101/11-34-002-26W3/04] (NAH Battle Creek DD 1C11-34-2B14-34-2-26)</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6002</v>
+        <v>6086</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -7833,14 +7833,14 @@
         <v>30</v>
       </c>
       <c r="V105" t="n">
-        <v>49.25465</v>
+        <v>49.17016</v>
       </c>
       <c r="W105" t="n">
-        <v>-109.48226</v>
+        <v>-109.40476</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6086</t>
         </is>
       </c>
     </row>
@@ -7850,11 +7850,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-03-017-14W3/00] (Canadian Helium Wilhelm 14-3-17-14)</t>
+          <t>Deadwood Formation Helium Production Well [121/07-09-017-14W3/00] (Gulf Sask Landing Wilhelm 7 9 17 14)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6021</v>
+        <v>6088</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I106" t="b">
@@ -7903,14 +7903,14 @@
         <v>30</v>
       </c>
       <c r="V106" t="n">
-        <v>50.41137</v>
+        <v>50.41642</v>
       </c>
       <c r="W106" t="n">
-        <v>-107.85382</v>
+        <v>-107.87088</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6088</t>
         </is>
       </c>
     </row>
@@ -7920,11 +7920,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/01-09-017-14W3/00] (B.A. Wilhelm 1 A 9)</t>
+          <t>Fusilier North Mine</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5550</v>
+        <v>4331</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7973,14 +7973,14 @@
         <v>30</v>
       </c>
       <c r="V107" t="n">
-        <v>50.41339</v>
+        <v>51.91661</v>
       </c>
       <c r="W107" t="n">
-        <v>-107.86357</v>
+        <v>-109.79822</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
         </is>
       </c>
     </row>
@@ -7990,11 +7990,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-14-004-09W3/00] (NAH Mankota West DD 4A16-14-1C16-14-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [141/02-09-017-14W3/00] (IAC Wilhelm 2-9-17-14)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6019</v>
+        <v>5549</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -8043,14 +8043,14 @@
         <v>30</v>
       </c>
       <c r="V108" t="n">
-        <v>49.30389</v>
+        <v>50.41544</v>
       </c>
       <c r="W108" t="n">
-        <v>-107.10893</v>
+        <v>-107.86935</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
         </is>
       </c>
     </row>
@@ -8060,11 +8060,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [141/02-09-017-14W3/00] (IAC Wilhelm 2-9-17-14)</t>
+          <t>Deadwood Formation Helium Production Well [102/01-09-017-14W3/00] (B.A. Wilhelm 1 A 9)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5549</v>
+        <v>5550</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8113,14 +8113,14 @@
         <v>30</v>
       </c>
       <c r="V109" t="n">
-        <v>50.41544</v>
+        <v>50.41339</v>
       </c>
       <c r="W109" t="n">
-        <v>-107.86935</v>
+        <v>-107.86357</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
         </is>
       </c>
     </row>
@@ -8130,11 +8130,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/12-25-004-09W3/00] (NAH Mankota DD 4D8-26-1B12-25-4-9)</t>
+          <t>Souris River Formation Helium Production Well [141/05-31-003-26W3/00] (Interex Battle Creek West 5-31-3-26)</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6020</v>
+        <v>5558</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -8183,14 +8183,14 @@
         <v>30</v>
       </c>
       <c r="V110" t="n">
-        <v>49.32802</v>
+        <v>49.25304</v>
       </c>
       <c r="W110" t="n">
-        <v>-107.10274</v>
+        <v>-109.50042</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5558</t>
         </is>
       </c>
     </row>

--- a/site/sk_leads.xlsx
+++ b/site/sk_leads.xlsx
@@ -570,22 +570,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fond Du Lac Uranium Deposit</t>
+          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1572</v>
+        <v>5996</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Uranium, Iron</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -623,14 +623,14 @@
         <v>38</v>
       </c>
       <c r="V2" t="n">
-        <v>59.30417</v>
+        <v>49.56951</v>
       </c>
       <c r="W2" t="n">
-        <v>-107.16668</v>
+        <v>-103.14392</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
         </is>
       </c>
     </row>
@@ -710,11 +710,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [02-22-007-09W2]</t>
+          <t>Duperow Formation Lithium Exploration Well [04-15-032-23W3]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5996</v>
+        <v>6076</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -763,14 +763,14 @@
         <v>38</v>
       </c>
       <c r="V4" t="n">
-        <v>49.56951</v>
+        <v>51.73895</v>
       </c>
       <c r="W4" t="n">
-        <v>-103.14392</v>
+        <v>-109.19123</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5996</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6076</t>
         </is>
       </c>
     </row>
@@ -780,22 +780,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duperow Formation Lithium Exploration Well [04-15-032-23W3]</t>
+          <t>Deep Bay Graphite Deposit</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6076</v>
+        <v>480</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lithium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -833,14 +833,14 @@
         <v>38</v>
       </c>
       <c r="V5" t="n">
-        <v>51.73895</v>
+        <v>56.38334</v>
       </c>
       <c r="W5" t="n">
-        <v>-109.19123</v>
+        <v>-103.12501</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
         </is>
       </c>
     </row>
@@ -850,22 +850,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deep Bay Graphite Deposit</t>
+          <t>Fond Du Lac Uranium Deposit</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>480</v>
+        <v>1572</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Uranium, Iron</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -903,14 +903,14 @@
         <v>38</v>
       </c>
       <c r="V6" t="n">
-        <v>56.38334</v>
+        <v>59.30417</v>
       </c>
       <c r="W6" t="n">
-        <v>-103.12501</v>
+        <v>-107.16668</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0480</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/1572</t>
         </is>
       </c>
     </row>
@@ -920,11 +920,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
+          <t>Gollier Creek Mine</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5547</v>
+        <v>2780</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Deposit: Advanced Exploration</t>
+          <t>Deposit: Development</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -973,14 +973,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>49.01463</v>
+        <v>49.41374</v>
       </c>
       <c r="W7" t="n">
-        <v>-109.73056</v>
+        <v>-106.24081</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
         </is>
       </c>
     </row>
@@ -990,11 +990,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basin Lake</t>
+          <t>Bitter Lake Deposit</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5043</v>
+        <v>3673</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,14 +1043,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>52.60621</v>
+        <v>50.10616</v>
       </c>
       <c r="W8" t="n">
-        <v>-105.2732</v>
+        <v>-109.79816</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
         </is>
       </c>
     </row>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Redberry Lake</t>
+          <t>Lydden Lake Deposit</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5044</v>
+        <v>3676</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Magnesium Sulphate</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1113,14 +1113,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>52.69009</v>
+        <v>52.01647</v>
       </c>
       <c r="W9" t="n">
-        <v>-107.16763</v>
+        <v>-108.36644</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
         </is>
       </c>
     </row>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eins Lake</t>
+          <t>Estevan Brick Kaolin 1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4369</v>
+        <v>3849</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1183,14 +1183,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>52.04888</v>
+        <v>49.52546</v>
       </c>
       <c r="W10" t="n">
-        <v>-108.51676</v>
+        <v>-108.84275</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
         </is>
       </c>
     </row>
@@ -1200,11 +1200,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BA Wilhelm 1-9</t>
+          <t>Estevan Brick Kaolin 2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4312</v>
+        <v>3861</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1253,14 +1253,14 @@
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>50.41172</v>
+        <v>49.50293</v>
       </c>
       <c r="W11" t="n">
-        <v>-107.86309</v>
+        <v>-109.01845</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
         </is>
       </c>
     </row>
@@ -1270,11 +1270,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Talisman Bures 11-17-9-21</t>
+          <t>Wood Mountain Ridge Resource Area</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5548</v>
+        <v>3972</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1323,14 +1323,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>49.73459</v>
+        <v>49.41751</v>
       </c>
       <c r="W12" t="n">
-        <v>-104.81905</v>
+        <v>-106.3298</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
         </is>
       </c>
     </row>
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEML et al Bigstick 6-14-13-26</t>
+          <t>Waverly Ridge Resource Area</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5551</v>
+        <v>3973</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin, Silica Sand</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1393,14 +1393,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>50.08028</v>
+        <v>49.36742</v>
       </c>
       <c r="W13" t="n">
-        <v>-109.45467</v>
+        <v>-106.49029</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
         </is>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
+          <t>Ingebrigt North Deposit</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5552</v>
+        <v>3669</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1463,14 +1463,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>49.34918</v>
+        <v>50.40828</v>
       </c>
       <c r="W14" t="n">
-        <v>-104.82203</v>
+        <v>-109.38439</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
         </is>
       </c>
     </row>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Canera Francis 6-36-12-15</t>
+          <t>Aroma Lake Deposit</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5553</v>
+        <v>3668</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1533,14 +1533,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>50.03521</v>
+        <v>52.29156</v>
       </c>
       <c r="W15" t="n">
-        <v>-103.9312</v>
+        <v>-108.55453</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
         </is>
       </c>
     </row>
@@ -1550,11 +1550,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lydden Lake Deposit</t>
+          <t>Rockglen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3676</v>
+        <v>3976</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sodium Sulphate, Magnesium Sulphate</t>
+          <t>Bentonite, Volcanic Ash</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1603,14 +1603,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>52.01647</v>
+        <v>49.19705</v>
       </c>
       <c r="W16" t="n">
-        <v>-108.36644</v>
+        <v>-106.03823</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3676</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wood Mountain Ridge Resource Area</t>
+          <t>Estevan Brick 72H-2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3972</v>
+        <v>4075</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1673,14 +1673,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>49.41751</v>
+        <v>49.57279</v>
       </c>
       <c r="W17" t="n">
-        <v>-106.3298</v>
+        <v>-105.74453</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3972</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
         </is>
       </c>
     </row>
@@ -1690,11 +1690,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eastend Resource Area</t>
+          <t>Estevan Brick 72H-5</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3866</v>
+        <v>4078</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
@@ -1743,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="V18" t="n">
-        <v>49.40637</v>
+        <v>49.63023</v>
       </c>
       <c r="W18" t="n">
-        <v>-108.62578</v>
+        <v>-105.81014</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
         </is>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 2</t>
+          <t>Estevan Brick 72H-6</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3861</v>
+        <v>4079</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
@@ -1813,14 +1813,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>49.50293</v>
+        <v>49.61548</v>
       </c>
       <c r="W19" t="n">
-        <v>-109.01845</v>
+        <v>-105.81093</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3861</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1830,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rockglen</t>
+          <t>Eins Lake</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3976</v>
+        <v>4369</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bentonite, Volcanic Ash</t>
+          <t>Sodium Sulphate, Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1883,14 +1883,14 @@
         <v>35</v>
       </c>
       <c r="V20" t="n">
-        <v>49.19705</v>
+        <v>52.04888</v>
       </c>
       <c r="W20" t="n">
-        <v>-106.03823</v>
+        <v>-108.51676</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3976</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4369</t>
         </is>
       </c>
     </row>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Waverly Ridge Resource Area</t>
+          <t>BA Wilhelm 1-9</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3973</v>
+        <v>4312</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kaolin, Silica Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1953,14 +1953,14 @@
         <v>35</v>
       </c>
       <c r="V21" t="n">
-        <v>49.36742</v>
+        <v>50.41172</v>
       </c>
       <c r="W21" t="n">
-        <v>-106.49029</v>
+        <v>-107.86309</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3973</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4312</t>
         </is>
       </c>
     </row>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-6</t>
+          <t>Berkley et al Hardy S DD 8C3-6-3C3-6-5-21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4079</v>
+        <v>5552</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2023,14 +2023,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>49.61548</v>
+        <v>49.34918</v>
       </c>
       <c r="W22" t="n">
-        <v>-105.81093</v>
+        <v>-104.82203</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4079</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5552</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2040,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-5</t>
+          <t>Canera Francis 6-36-12-15</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4078</v>
+        <v>5553</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2093,14 +2093,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>49.63023</v>
+        <v>50.03521</v>
       </c>
       <c r="W23" t="n">
-        <v>-105.81014</v>
+        <v>-103.9312</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5553</t>
         </is>
       </c>
     </row>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-2</t>
+          <t>DEML et al Bigstick 6-14-13-26</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4075</v>
+        <v>5551</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2163,14 +2163,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>49.57279</v>
+        <v>50.08028</v>
       </c>
       <c r="W24" t="n">
-        <v>-105.74453</v>
+        <v>-109.45467</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4075</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5551</t>
         </is>
       </c>
     </row>
@@ -2180,11 +2180,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Axe Lake Deposit</t>
+          <t>Pine Cliff Willow Creek 2A-7-1-28</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2784</v>
+        <v>5547</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Oil Sand</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2233,14 +2233,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>57.20387</v>
+        <v>49.01463</v>
       </c>
       <c r="W25" t="n">
-        <v>-109.9058</v>
+        <v>-109.73056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5547</t>
         </is>
       </c>
     </row>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gollier Creek Mine</t>
+          <t>Talisman Bures 11-17-9-21</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2780</v>
+        <v>5548</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Deposit: Development</t>
+          <t>Deposit: Advanced Exploration</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2303,14 +2303,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>49.41374</v>
+        <v>49.73459</v>
       </c>
       <c r="W26" t="n">
-        <v>-106.24081</v>
+        <v>-104.81905</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2780</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5548</t>
         </is>
       </c>
     </row>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sybouts West Deposit</t>
+          <t>Redberry Lake</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3672</v>
+        <v>5044</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2373,14 +2373,14 @@
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>49.04192</v>
+        <v>52.69009</v>
       </c>
       <c r="W27" t="n">
-        <v>-104.53479</v>
+        <v>-107.16763</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5044</t>
         </is>
       </c>
     </row>
@@ -2390,11 +2390,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bitter Lake Deposit</t>
+          <t>Basin Lake</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3673</v>
+        <v>5043</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Magnesium Sulphate</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2443,14 +2443,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>50.10616</v>
+        <v>52.60621</v>
       </c>
       <c r="W28" t="n">
-        <v>-109.79816</v>
+        <v>-105.2732</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3673</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5043</t>
         </is>
       </c>
     </row>
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aroma Lake Deposit</t>
+          <t>Eastend Resource Area</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3668</v>
+        <v>3866</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2513,14 +2513,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>52.29156</v>
+        <v>49.40637</v>
       </c>
       <c r="W29" t="n">
-        <v>-108.55453</v>
+        <v>-108.62578</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3668</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3866</t>
         </is>
       </c>
     </row>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Estevan Brick Kaolin 1</t>
+          <t>Verlo East Deposit</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3849</v>
+        <v>3671</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2583,14 +2583,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>49.52546</v>
+        <v>50.33614</v>
       </c>
       <c r="W30" t="n">
-        <v>-108.84275</v>
+        <v>-108.45696</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3849</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
         </is>
       </c>
     </row>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ingebrigt North Deposit</t>
+          <t>Sybouts West Deposit</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3669</v>
+        <v>3672</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
@@ -2653,14 +2653,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>50.40828</v>
+        <v>49.04192</v>
       </c>
       <c r="W31" t="n">
-        <v>-109.38439</v>
+        <v>-104.53479</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3669</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3672</t>
         </is>
       </c>
     </row>
@@ -2670,11 +2670,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Verlo East Deposit</t>
+          <t>C28 Kimberlite</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3671</v>
+        <v>2864</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2723,14 +2723,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>50.33614</v>
+        <v>53.70316</v>
       </c>
       <c r="W32" t="n">
-        <v>-108.45696</v>
+        <v>-104.85739</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
         </is>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C28 Kimberlite</t>
+          <t>Axe Lake Deposit</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2864</v>
+        <v>2784</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Oil Sand</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2793,14 +2793,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>53.70316</v>
+        <v>57.20387</v>
       </c>
       <c r="W33" t="n">
-        <v>-104.85739</v>
+        <v>-109.9058</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2864</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2784</t>
         </is>
       </c>
     </row>
@@ -2810,11 +2810,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-36-003-27W3/00] (NAH Battle Creek DD 3C6-36-3B6-36-3-27W3)</t>
+          <t>Souris River Formation Helium Production Well [101/15-09-005-21W3/02] (North American Helium Whitemud 15-9)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6081</v>
+        <v>6087</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -2863,14 +2863,14 @@
         <v>30</v>
       </c>
       <c r="V34" t="n">
-        <v>49.252</v>
+        <v>49.3769</v>
       </c>
       <c r="W34" t="n">
-        <v>-109.51999</v>
+        <v>-108.76953</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6081</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6087</t>
         </is>
       </c>
     </row>
@@ -2880,11 +2880,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/15-35-009-11W3/00] (North American Helium Ponteix 15-35-9-11)</t>
+          <t>Truax Quarry</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6010</v>
+        <v>2782</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Bentonite</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I35" t="b">
@@ -2933,14 +2933,14 @@
         <v>30</v>
       </c>
       <c r="V35" t="n">
-        <v>49.78513</v>
+        <v>49.96019</v>
       </c>
       <c r="W35" t="n">
-        <v>-107.39009</v>
+        <v>-104.81877</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-30-003-26W3/00] (North American Helium Battle Creek W 6-3)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-09-006-22W3/00] (NAH Eastend 14-9-6-22)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6003</v>
+        <v>6085</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
@@ -3003,14 +3003,14 @@
         <v>30</v>
       </c>
       <c r="V36" t="n">
-        <v>49.23862</v>
+        <v>49.46254</v>
       </c>
       <c r="W36" t="n">
-        <v>-109.49394</v>
+        <v>-108.90993</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6085</t>
         </is>
       </c>
     </row>
@@ -3020,11 +3020,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/09-31-003-26W3/00] (North American Helium Battle Creek 9-31-3-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-07-016-16W3/00] (NAH Antelope Lake DD 2C14-7-1B14-7-16-16)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6002</v>
+        <v>6082</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
@@ -3073,14 +3073,14 @@
         <v>30</v>
       </c>
       <c r="V37" t="n">
-        <v>49.25465</v>
+        <v>50.33577</v>
       </c>
       <c r="W37" t="n">
-        <v>-109.48226</v>
+        <v>-108.19537</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6082</t>
         </is>
       </c>
     </row>
@@ -3090,11 +3090,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-28-009-11W3/00] (NAH Cadillac DD 1D16-28-1D16-28-9-11)</t>
+          <t>Deadwood Formation Helium Production Well [101/02-18-016-16W3/00] (NAH Antelope Lake DD 1C2-18-3D2-18-16-16)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6008</v>
+        <v>6084</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
@@ -3143,14 +3143,14 @@
         <v>30</v>
       </c>
       <c r="V38" t="n">
-        <v>49.76938</v>
+        <v>50.34284</v>
       </c>
       <c r="W38" t="n">
-        <v>-107.42801</v>
+        <v>-108.18985</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6084</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/06-35-009-11W3/00] (NAH Cadillac DD 2A11-35-3D6-35-9-11)</t>
+          <t>Deadwood Formation Helium Production Well [101/02-17-016-16W3/00] (NAH Antelope Lake DD 4A2-17-4D2-17-16-16)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6009</v>
+        <v>6083</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
@@ -3213,14 +3213,14 @@
         <v>30</v>
       </c>
       <c r="V39" t="n">
-        <v>49.77879</v>
+        <v>50.342</v>
       </c>
       <c r="W39" t="n">
-        <v>-107.39509</v>
+        <v>-108.16593</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6083</t>
         </is>
       </c>
     </row>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/11-34-009-11W3/00] (NAH Cadillac DD 4A8-33-3B11-34-9-11)</t>
+          <t>Deadwood Formation Helium Production Well [121/07-09-017-14W3/00] (Gulf Sask Landing Wilhelm 7 9 17 14)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6006</v>
+        <v>6088</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3283,14 +3283,14 @@
         <v>30</v>
       </c>
       <c r="V40" t="n">
-        <v>49.77938</v>
+        <v>50.41642</v>
       </c>
       <c r="W40" t="n">
-        <v>-107.42112</v>
+        <v>-107.87088</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6088</t>
         </is>
       </c>
     </row>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-27-009-11W3/00] (NAH Cadillac 16-27-9-11W3)</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [101/11-34-002-26W3/04] (NAH Battle Creek DD 1C11-34-2B14-34-2-26)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6005</v>
+        <v>6086</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
@@ -3353,14 +3353,14 @@
         <v>30</v>
       </c>
       <c r="V41" t="n">
-        <v>49.77022</v>
+        <v>49.17016</v>
       </c>
       <c r="W41" t="n">
-        <v>-107.40787</v>
+        <v>-109.40476</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6086</t>
         </is>
       </c>
     </row>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [102/10-09-006-22W3/00] (North American Helium Eastend 10B-9-6-22)</t>
+          <t>Wapaw Bay Mine</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6004</v>
+        <v>671</v>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Leonardite, Coal (Non-Metallurgical)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3414,23 +3414,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U42" t="n">
         <v>30</v>
       </c>
       <c r="V42" t="n">
-        <v>49.46027</v>
+        <v>54.86112</v>
       </c>
       <c r="W42" t="n">
-        <v>-108.90729</v>
+        <v>-104.66112</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
         </is>
       </c>
     </row>
@@ -3440,11 +3440,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/01-03-010-11W3/00] (NAH Cadillac DD 3C4-2-1C1-3-10-11)</t>
+          <t>Willow Bunch Clinker Shale Mine</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6007</v>
+        <v>2781</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Clinker</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I43" t="b">
@@ -3493,14 +3493,14 @@
         <v>30</v>
       </c>
       <c r="V43" t="n">
-        <v>49.78761</v>
+        <v>49.32932</v>
       </c>
       <c r="W43" t="n">
-        <v>-107.40843</v>
+        <v>-105.52988</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
         </is>
       </c>
     </row>
@@ -3510,11 +3510,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101-10-01-004-09W3/00] (NAH Mankota DD 3C9-1-2A10-1-4-9)</t>
+          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [102/03-35-005-27W3/04] (NAH Consul DD 1C2-35-2C2-35-5-27)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6079</v>
+        <v>6012</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
@@ -3563,14 +3563,14 @@
         <v>30</v>
       </c>
       <c r="V44" t="n">
-        <v>49.26926</v>
+        <v>49.42389</v>
       </c>
       <c r="W44" t="n">
-        <v>-107.09053</v>
+        <v>-109.53802</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6079</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
         </is>
       </c>
     </row>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/09-35-003-09W3/00] (NAH Mankota DD 2C12-36-2A9-35-3-9)</t>
+          <t>Souris River Formation Helium Production Well [101/16-21-005-27W3/02] (NAH Consul 16A-21-5-27)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6080</v>
+        <v>6013</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
@@ -3633,14 +3633,14 @@
         <v>30</v>
       </c>
       <c r="V45" t="n">
-        <v>49.25484</v>
+        <v>49.40655</v>
       </c>
       <c r="W45" t="n">
-        <v>-107.10681</v>
+        <v>-109.5718</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6080</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
         </is>
       </c>
     </row>
@@ -3650,11 +3650,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-03-017-14W3/00] (Canadian Helium Wilhelm 14-3-17-14)</t>
+          <t>Deadwood Formation Helium Production Well [103/08-04-006-26W3/02] (NAH Cypress 4C8-4-6-26)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6021</v>
+        <v>6014</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3703,14 +3703,14 @@
         <v>30</v>
       </c>
       <c r="V46" t="n">
-        <v>50.41137</v>
+        <v>49.44309</v>
       </c>
       <c r="W46" t="n">
-        <v>-107.85382</v>
+        <v>-109.44006</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/10-36-003-09W3/02] (NAH Mankota DD 1C14-36-3C10-36-3-9)</t>
+          <t>Souris River Formation Helium Production Well [101/16-27-005-26W3/00] (NAH Cypress DD 1B1-34-4C16-27-5-26)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6078</v>
+        <v>6015</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3773,14 +3773,14 @@
         <v>30</v>
       </c>
       <c r="V47" t="n">
-        <v>49.25803</v>
+        <v>49.42103</v>
       </c>
       <c r="W47" t="n">
-        <v>-107.09301</v>
+        <v>-109.41718</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6078</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
         </is>
       </c>
     </row>
@@ -3790,11 +3790,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/12-25-004-09W3/00] (NAH Mankota DD 4D8-26-1B12-25-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [102/14-34-005-26W3/00] (NAH Cypress 14-34-5-26)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6020</v>
+        <v>6016</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
         <v>30</v>
       </c>
       <c r="V48" t="n">
-        <v>49.32802</v>
+        <v>49.43366</v>
       </c>
       <c r="W48" t="n">
-        <v>-107.10274</v>
+        <v>-109.4287</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
         </is>
       </c>
     </row>
@@ -3860,11 +3860,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-14-004-09W3/00] (NAH Mankota West DD 4A16-14-1C16-14-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/05-26-004-09W3/00] (NAH Mankota DD 2D5-26-4C5-26-4-9)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6019</v>
+        <v>6017</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3913,14 +3913,14 @@
         <v>30</v>
       </c>
       <c r="V49" t="n">
-        <v>49.30389</v>
+        <v>49.32636</v>
       </c>
       <c r="W49" t="n">
-        <v>-107.10893</v>
+        <v>-107.12461</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
         </is>
       </c>
     </row>
@@ -3930,11 +3930,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/05-26-004-09W3/00] (NAH Mankota DD 2D5-26-4C5-26-4-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-15-004-09W3/00] (NAH Mankota West DD 1D16-15-2D16-15-4-9)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6017</v>
+        <v>6018</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
@@ -3983,14 +3983,14 @@
         <v>30</v>
       </c>
       <c r="V50" t="n">
-        <v>49.32636</v>
+        <v>49.3046</v>
       </c>
       <c r="W50" t="n">
-        <v>-107.12461</v>
+        <v>-107.12846</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6017</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
         </is>
       </c>
     </row>
@@ -4000,11 +4000,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/16-15-004-09W3/00] (NAH Mankota West DD 1D16-15-2D16-15-4-9)</t>
+          <t>Souris River Formation Helium Production Well [102/10-09-006-22W3/00] (North American Helium Eastend 10B-9-6-22)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6018</v>
+        <v>6004</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -4053,14 +4053,14 @@
         <v>30</v>
       </c>
       <c r="V51" t="n">
-        <v>49.3046</v>
+        <v>49.46027</v>
       </c>
       <c r="W51" t="n">
-        <v>-107.12846</v>
+        <v>-108.90729</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6018</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6004</t>
         </is>
       </c>
     </row>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [103/08-04-006-26W3/02] (NAH Cypress 4C8-4-6-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-27-009-11W3/00] (NAH Cadillac 16-27-9-11W3)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6014</v>
+        <v>6005</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -4123,14 +4123,14 @@
         <v>30</v>
       </c>
       <c r="V52" t="n">
-        <v>49.44309</v>
+        <v>49.77022</v>
       </c>
       <c r="W52" t="n">
-        <v>-109.44006</v>
+        <v>-107.40787</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6014</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6005</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/16-21-005-27W3/02] (NAH Consul 16A-21-5-27)</t>
+          <t>Deadwood Formation Helium Production Well [101/11-34-009-11W3/00] (NAH Cadillac DD 4A8-33-3B11-34-9-11)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6013</v>
+        <v>6006</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -4193,14 +4193,14 @@
         <v>30</v>
       </c>
       <c r="V53" t="n">
-        <v>49.40655</v>
+        <v>49.77938</v>
       </c>
       <c r="W53" t="n">
-        <v>-109.5718</v>
+        <v>-107.42112</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6013</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6006</t>
         </is>
       </c>
     </row>
@@ -4210,11 +4210,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/14-34-005-26W3/00] (NAH Cypress 14-34-5-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/01-03-010-11W3/00] (NAH Cadillac DD 3C4-2-1C1-3-10-11)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6016</v>
+        <v>6007</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
@@ -4263,14 +4263,14 @@
         <v>30</v>
       </c>
       <c r="V54" t="n">
-        <v>49.43366</v>
+        <v>49.78761</v>
       </c>
       <c r="W54" t="n">
-        <v>-109.4287</v>
+        <v>-107.40843</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6016</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6007</t>
         </is>
       </c>
     </row>
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/16-27-005-26W3/00] (NAH Cypress DD 1B1-34-4C16-27-5-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-28-009-11W3/00] (NAH Cadillac DD 1D16-28-1D16-28-9-11)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6015</v>
+        <v>6008</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
@@ -4333,14 +4333,14 @@
         <v>30</v>
       </c>
       <c r="V55" t="n">
-        <v>49.42103</v>
+        <v>49.76938</v>
       </c>
       <c r="W55" t="n">
-        <v>-109.41718</v>
+        <v>-107.42801</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6015</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6008</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [102/03-35-005-27W3/04] (NAH Consul DD 1C2-35-2C2-35-5-27)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-35-009-11W3/00] (NAH Cadillac DD 2A11-35-3D6-35-9-11)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6012</v>
+        <v>6009</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
@@ -4403,14 +4403,14 @@
         <v>30</v>
       </c>
       <c r="V56" t="n">
-        <v>49.42389</v>
+        <v>49.77879</v>
       </c>
       <c r="W56" t="n">
-        <v>-109.53802</v>
+        <v>-107.39509</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6012</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6009</t>
         </is>
       </c>
     </row>
@@ -4420,11 +4420,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Truax Quarry</t>
+          <t>Deadwood Formation Helium Production Well [102/15-35-009-11W3/00] (North American Helium Ponteix 15-35-9-11)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2782</v>
+        <v>6010</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bentonite</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -4473,14 +4473,14 @@
         <v>30</v>
       </c>
       <c r="V57" t="n">
-        <v>49.96019</v>
+        <v>49.78513</v>
       </c>
       <c r="W57" t="n">
-        <v>-104.81877</v>
+        <v>-107.39009</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2782</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6010</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-09-006-22W3/00] (NAH Eastend 14-9-6-22)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-36-003-27W3/00] (NAH Battle Creek DD 3C6-36-3B6-36-3-27W3)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6085</v>
+        <v>6081</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
@@ -4613,14 +4613,14 @@
         <v>30</v>
       </c>
       <c r="V59" t="n">
-        <v>49.46254</v>
+        <v>49.252</v>
       </c>
       <c r="W59" t="n">
-        <v>-108.90993</v>
+        <v>-109.51999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6085</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6081</t>
         </is>
       </c>
     </row>
@@ -4630,11 +4630,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/03-10-017-14W3/00] (B A Sask Lndg Wilhelm 3 10 17 14)</t>
+          <t>Deadwood Formation Helium Production Well [101-10-01-004-09W3/00] (NAH Mankota DD 3C9-1-2A10-1-4-9)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4313</v>
+        <v>6079</v>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -4683,14 +4683,14 @@
         <v>30</v>
       </c>
       <c r="V60" t="n">
-        <v>50.41372</v>
+        <v>49.26926</v>
       </c>
       <c r="W60" t="n">
-        <v>-107.85215</v>
+        <v>-107.09053</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6079</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Estevan Brick 72G Quarry</t>
+          <t>Deadwood Formation Helium Production Well [101/12-10-005-08W3/00] (CVE Mankota 12-10-5-8)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3974</v>
+        <v>4063</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4823,14 +4823,14 @@
         <v>30</v>
       </c>
       <c r="V62" t="n">
-        <v>49.20739</v>
+        <v>49.37259</v>
       </c>
       <c r="W62" t="n">
-        <v>-106.06351</v>
+        <v>-107.01264</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
         </is>
       </c>
     </row>
@@ -4910,11 +4910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ravenscrag Quarry</t>
+          <t>Plainsman Quarry 3</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3865</v>
+        <v>3863</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
@@ -4963,14 +4963,14 @@
         <v>30</v>
       </c>
       <c r="V64" t="n">
-        <v>49.49081</v>
+        <v>49.51582</v>
       </c>
       <c r="W64" t="n">
-        <v>-109.14115</v>
+        <v>-109.01757</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
         </is>
       </c>
     </row>
@@ -5050,11 +5050,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 3</t>
+          <t>Estevan Brick 72G Quarry</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3863</v>
+        <v>3974</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
@@ -5103,14 +5103,14 @@
         <v>30</v>
       </c>
       <c r="V66" t="n">
-        <v>49.51582</v>
+        <v>49.20739</v>
       </c>
       <c r="W66" t="n">
-        <v>-109.01757</v>
+        <v>-106.06351</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3863</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3974</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Day Quarry</t>
+          <t>Knolly Quarry</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3857</v>
+        <v>3855</v>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
@@ -5173,14 +5173,14 @@
         <v>30</v>
       </c>
       <c r="V67" t="n">
-        <v>49.51123</v>
+        <v>49.46895</v>
       </c>
       <c r="W67" t="n">
-        <v>-108.84032</v>
+        <v>-108.92433</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
         </is>
       </c>
     </row>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Knolly Quarry</t>
+          <t>I-XL Industries 1 Quarry</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3855</v>
+        <v>3853</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
@@ -5313,14 +5313,14 @@
         <v>30</v>
       </c>
       <c r="V69" t="n">
-        <v>49.46895</v>
+        <v>49.46928</v>
       </c>
       <c r="W69" t="n">
-        <v>-108.92433</v>
+        <v>-108.83703</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3855</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
         </is>
       </c>
     </row>
@@ -5330,11 +5330,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>I-XL Industries 1 Quarry</t>
+          <t>Day Quarry</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3853</v>
+        <v>3857</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
@@ -5383,14 +5383,14 @@
         <v>30</v>
       </c>
       <c r="V70" t="n">
-        <v>49.46928</v>
+        <v>49.51123</v>
       </c>
       <c r="W70" t="n">
-        <v>-108.83703</v>
+        <v>-108.84032</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3853</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3857</t>
         </is>
       </c>
     </row>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Plainsman Quarry 1</t>
+          <t>Old Pit Quarry</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3860</v>
+        <v>3858</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
@@ -5523,14 +5523,14 @@
         <v>30</v>
       </c>
       <c r="V72" t="n">
-        <v>49.49048</v>
+        <v>49.47594</v>
       </c>
       <c r="W72" t="n">
-        <v>-109.04754</v>
+        <v>-109.01306</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Old Pit Quarry</t>
+          <t>Ravenscrag Quarry</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3858</v>
+        <v>3865</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
@@ -5663,14 +5663,14 @@
         <v>30</v>
       </c>
       <c r="V74" t="n">
-        <v>49.47594</v>
+        <v>49.49081</v>
       </c>
       <c r="W74" t="n">
-        <v>-109.01306</v>
+        <v>-109.14115</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3858</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3865</t>
         </is>
       </c>
     </row>
@@ -5680,11 +5680,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 2</t>
+          <t>Ceylon Lake Deposit</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3690</v>
+        <v>3670</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5733,14 +5733,14 @@
         <v>30</v>
       </c>
       <c r="V75" t="n">
-        <v>49.12208</v>
+        <v>49.28985</v>
       </c>
       <c r="W75" t="n">
-        <v>-103.07029</v>
+        <v>-104.70435</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
         </is>
       </c>
     </row>
@@ -5820,11 +5820,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dempster Clay Pit</t>
+          <t>Estevan Brick Location 2</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3851</v>
+        <v>3690</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
@@ -5873,14 +5873,14 @@
         <v>30</v>
       </c>
       <c r="V77" t="n">
-        <v>49.52823</v>
+        <v>49.12208</v>
       </c>
       <c r="W77" t="n">
-        <v>-108.84206</v>
+        <v>-103.07029</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3690</t>
         </is>
       </c>
     </row>
@@ -5890,11 +5890,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Estevan Brick Location 1</t>
+          <t>Dempster Clay Pit</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3689</v>
+        <v>3851</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
@@ -5943,14 +5943,14 @@
         <v>30</v>
       </c>
       <c r="V78" t="n">
-        <v>49.06449</v>
+        <v>49.52823</v>
       </c>
       <c r="W78" t="n">
-        <v>-103.06979</v>
+        <v>-108.84206</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3851</t>
         </is>
       </c>
     </row>
@@ -5960,11 +5960,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ceylon Lake Deposit</t>
+          <t>Estevan Brick Location 1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3670</v>
+        <v>3689</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6013,14 +6013,14 @@
         <v>30</v>
       </c>
       <c r="V79" t="n">
-        <v>49.28985</v>
+        <v>49.06449</v>
       </c>
       <c r="W79" t="n">
-        <v>-104.70435</v>
+        <v>-103.06979</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3670</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3689</t>
         </is>
       </c>
     </row>
@@ -6030,11 +6030,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Snakehole Lake Mine</t>
+          <t>Frederick Lake Mine</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
@@ -6083,14 +6083,14 @@
         <v>30</v>
       </c>
       <c r="V80" t="n">
-        <v>50.50916</v>
+        <v>50.00971</v>
       </c>
       <c r="W80" t="n">
-        <v>-108.47667</v>
+        <v>-105.77947</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frederick Lake Mine</t>
+          <t>Chaplin Mine</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3664</v>
+        <v>3657</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I81" t="b">
@@ -6153,14 +6153,14 @@
         <v>30</v>
       </c>
       <c r="V81" t="n">
-        <v>50.00971</v>
+        <v>50.46073</v>
       </c>
       <c r="W81" t="n">
-        <v>-105.77947</v>
+        <v>-106.66983</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3664</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sybouts East Mine</t>
+          <t>Alsask Lake Mine</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3662</v>
+        <v>3661</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -6223,14 +6223,14 @@
         <v>30</v>
       </c>
       <c r="V82" t="n">
-        <v>49.03697</v>
+        <v>51.33929</v>
       </c>
       <c r="W82" t="n">
-        <v>-104.43359</v>
+        <v>-109.86516</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
         </is>
       </c>
     </row>
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alsask Lake Mine</t>
+          <t>Ingebrigt South Mine</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3661</v>
+        <v>3660</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -6293,14 +6293,14 @@
         <v>30</v>
       </c>
       <c r="V83" t="n">
-        <v>51.33929</v>
+        <v>50.35665</v>
       </c>
       <c r="W83" t="n">
-        <v>-109.86516</v>
+        <v>-109.32196</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3661</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
         </is>
       </c>
     </row>
@@ -6310,11 +6310,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ingebrigt South Mine</t>
+          <t>Horseshoe Lake Mine</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
@@ -6363,14 +6363,14 @@
         <v>30</v>
       </c>
       <c r="V84" t="n">
-        <v>50.35665</v>
+        <v>49.71947</v>
       </c>
       <c r="W84" t="n">
-        <v>-109.32196</v>
+        <v>-105.35516</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3660</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
         </is>
       </c>
     </row>
@@ -6380,11 +6380,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Horseshoe Lake Mine</t>
+          <t>Sybouts East Mine</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3659</v>
+        <v>3662</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
@@ -6433,14 +6433,14 @@
         <v>30</v>
       </c>
       <c r="V85" t="n">
-        <v>49.71947</v>
+        <v>49.03697</v>
       </c>
       <c r="W85" t="n">
-        <v>-105.35516</v>
+        <v>-104.43359</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3659</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3662</t>
         </is>
       </c>
     </row>
@@ -6450,11 +6450,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chaplin Mine</t>
+          <t>Snakehole Lake Mine</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3657</v>
+        <v>3666</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I86" t="b">
@@ -6503,14 +6503,14 @@
         <v>30</v>
       </c>
       <c r="V86" t="n">
-        <v>50.46073</v>
+        <v>50.50916</v>
       </c>
       <c r="W86" t="n">
-        <v>-106.66983</v>
+        <v>-108.47667</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3657</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3666</t>
         </is>
       </c>
     </row>
@@ -6520,11 +6520,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Willow Bunch Clinker Shale Mine</t>
+          <t>Plainsman Quarry 1</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2781</v>
+        <v>3860</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Clinker</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6573,14 +6573,14 @@
         <v>30</v>
       </c>
       <c r="V87" t="n">
-        <v>49.32932</v>
+        <v>49.49048</v>
       </c>
       <c r="W87" t="n">
-        <v>-105.52988</v>
+        <v>-109.04754</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/2781</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3860</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6590,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [101/15-09-005-21W3/02] (North American Helium Whitemud 15-9)</t>
+          <t>Deadwood Formation Helium Production Well [101/06-30-003-26W3/00] (North American Helium Battle Creek W 6-3)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6087</v>
+        <v>6003</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
@@ -6643,14 +6643,14 @@
         <v>30</v>
       </c>
       <c r="V88" t="n">
-        <v>49.3769</v>
+        <v>49.23862</v>
       </c>
       <c r="W88" t="n">
-        <v>-108.76953</v>
+        <v>-109.49394</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6087</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6003</t>
         </is>
       </c>
     </row>
@@ -6660,11 +6660,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/14-07-016-16W3/00] (NAH Antelope Lake DD 2C14-7-1B14-7-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/10-36-003-09W3/02] (NAH Mankota DD 1C14-36-3C10-36-3-9)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6082</v>
+        <v>6078</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -6713,14 +6713,14 @@
         <v>30</v>
       </c>
       <c r="V89" t="n">
-        <v>50.33577</v>
+        <v>49.25803</v>
       </c>
       <c r="W89" t="n">
-        <v>-108.19537</v>
+        <v>-107.09301</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6082</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6078</t>
         </is>
       </c>
     </row>
@@ -6730,11 +6730,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/02-17-016-16W3/00] (NAH Antelope Lake DD 4A2-17-4D2-17-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/03-10-017-14W3/00] (B A Sask Lndg Wilhelm 3 10 17 14)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6083</v>
+        <v>4313</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I90" t="b">
@@ -6783,14 +6783,14 @@
         <v>30</v>
       </c>
       <c r="V90" t="n">
-        <v>50.342</v>
+        <v>50.41372</v>
       </c>
       <c r="W90" t="n">
-        <v>-108.16593</v>
+        <v>-107.85215</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6083</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4313</t>
         </is>
       </c>
     </row>
@@ -6800,11 +6800,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-1 Quarry</t>
+          <t>Fusilier North Mine</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4074</v>
+        <v>4331</v>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Sodium Sulphate</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6853,14 +6853,14 @@
         <v>30</v>
       </c>
       <c r="V91" t="n">
-        <v>49.60125</v>
+        <v>51.91661</v>
       </c>
       <c r="W91" t="n">
-        <v>-105.74607</v>
+        <v>-109.79822</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
         </is>
       </c>
     </row>
@@ -6940,11 +6940,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Great Lakes Ceramics Quarry</t>
+          <t>Deadwood Formation Helium Production Well [102/10-25-003-27W3/00] (North American Helium Battle Creek 10-25-03-27W3)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3975</v>
+        <v>4060</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -6955,12 +6955,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I93" t="b">
@@ -6993,14 +6993,14 @@
         <v>30</v>
       </c>
       <c r="V93" t="n">
-        <v>49.20355</v>
+        <v>49.23949</v>
       </c>
       <c r="W93" t="n">
-        <v>-106.07015</v>
+        <v>-109.51141</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4060</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/12-10-005-08W3/00] (CVE Mankota 12-10-5-8)</t>
+          <t>Great Lakes Ceramics Quarry</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4063</v>
+        <v>3975</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7063,14 +7063,14 @@
         <v>30</v>
       </c>
       <c r="V94" t="n">
-        <v>49.37259</v>
+        <v>49.20355</v>
       </c>
       <c r="W94" t="n">
-        <v>-107.01264</v>
+        <v>-106.07015</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4063</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/3975</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Midland Mine</t>
+          <t>Estevan Brick 72H-1 Quarry</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -7133,14 +7133,14 @@
         <v>30</v>
       </c>
       <c r="V95" t="n">
-        <v>49.4577</v>
+        <v>49.60125</v>
       </c>
       <c r="W95" t="n">
-        <v>-105.64778</v>
+        <v>-105.74607</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4074</t>
         </is>
       </c>
     </row>
@@ -7150,11 +7150,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-4 Quarry</t>
+          <t>Midland Mine</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4077</v>
+        <v>4073</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -7203,14 +7203,14 @@
         <v>30</v>
       </c>
       <c r="V96" t="n">
-        <v>49.63087</v>
+        <v>49.4577</v>
       </c>
       <c r="W96" t="n">
-        <v>-105.78917</v>
+        <v>-105.64778</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4073</t>
         </is>
       </c>
     </row>
@@ -7220,11 +7220,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Estevan Brick 72H-3 Quarry</t>
+          <t>Estevan Brick 72H-4 Quarry</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
@@ -7273,14 +7273,14 @@
         <v>30</v>
       </c>
       <c r="V97" t="n">
-        <v>49.58841</v>
+        <v>49.63087</v>
       </c>
       <c r="W97" t="n">
-        <v>-105.79049</v>
+        <v>-105.78917</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4077</t>
         </is>
       </c>
     </row>
@@ -7290,11 +7290,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dominion Firebrick Quarry</t>
+          <t>Estevan Brick 72H-3 Quarry</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4287</v>
+        <v>4076</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -7343,14 +7343,14 @@
         <v>30</v>
       </c>
       <c r="V98" t="n">
-        <v>50.02441</v>
+        <v>49.58841</v>
       </c>
       <c r="W98" t="n">
-        <v>-105.22623</v>
+        <v>-105.79049</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4076</t>
         </is>
       </c>
     </row>
@@ -7360,11 +7360,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/10-25-003-27W3/00] (North American Helium Battle Creek 10-25-03-27W3)</t>
+          <t>I-XL Quarries</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4060</v>
+        <v>4286</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I99" t="b">
@@ -7413,14 +7413,14 @@
         <v>30</v>
       </c>
       <c r="V99" t="n">
-        <v>49.23949</v>
+        <v>50.00928</v>
       </c>
       <c r="W99" t="n">
-        <v>-109.51141</v>
+        <v>-105.15722</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4060</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7430,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>I-XL Quarries</t>
+          <t>Dominion Firebrick Quarry</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4286</v>
+        <v>4287</v>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
@@ -7483,14 +7483,14 @@
         <v>30</v>
       </c>
       <c r="V100" t="n">
-        <v>50.00928</v>
+        <v>50.02441</v>
       </c>
       <c r="W100" t="n">
-        <v>-105.15722</v>
+        <v>-105.22623</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4286</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4287</t>
         </is>
       </c>
     </row>
@@ -7500,11 +7500,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wapaw Bay Mine</t>
+          <t>A.P. Green Quarry</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>671</v>
+        <v>4288</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Leonardite, Coal (Non-Metallurgical)</t>
+          <t>Kaolin</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Deposit: Production</t>
+          <t>Deposit: Post-Production</t>
         </is>
       </c>
       <c r="I101" t="b">
@@ -7544,23 +7544,23 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T101" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U101" t="n">
         <v>30</v>
       </c>
       <c r="V101" t="n">
-        <v>54.86112</v>
+        <v>50.09003</v>
       </c>
       <c r="W101" t="n">
-        <v>-104.66112</v>
+        <v>-105.43064</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/0671</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
         </is>
       </c>
     </row>
@@ -7570,11 +7570,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A.P. Green Quarry</t>
+          <t>Deadwood Formation Helium Production Well [111/11-03-017-14W3/00] (Gulf Wilhelm11-3-17-14)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4288</v>
+        <v>4311</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Kaolin</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7623,14 +7623,14 @@
         <v>30</v>
       </c>
       <c r="V102" t="n">
-        <v>50.09003</v>
+        <v>50.40618</v>
       </c>
       <c r="W102" t="n">
-        <v>-105.43064</v>
+        <v>-107.85048</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4288</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
         </is>
       </c>
     </row>
@@ -7640,11 +7640,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [111/11-03-017-14W3/00] (Gulf Wilhelm11-3-17-14)</t>
+          <t>Souris River Formation Helium Production Well [141/05-31-003-26W3/00] (Interex Battle Creek West 5-31-3-26)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4311</v>
+        <v>5558</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I103" t="b">
@@ -7693,14 +7693,14 @@
         <v>30</v>
       </c>
       <c r="V103" t="n">
-        <v>50.40618</v>
+        <v>49.25304</v>
       </c>
       <c r="W103" t="n">
-        <v>-107.85048</v>
+        <v>-109.50042</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4311</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5558</t>
         </is>
       </c>
     </row>
@@ -7710,11 +7710,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [101/02-18-016-16W3/00] (NAH Antelope Lake DD 1C2-18-3D2-18-16-16)</t>
+          <t>Deadwood Formation Helium Production Well [101/09-35-003-09W3/00] (NAH Mankota DD 2C12-36-2A9-35-3-9)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6084</v>
+        <v>6080</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
@@ -7763,14 +7763,14 @@
         <v>30</v>
       </c>
       <c r="V104" t="n">
-        <v>50.34284</v>
+        <v>49.25484</v>
       </c>
       <c r="W104" t="n">
-        <v>-108.18985</v>
+        <v>-107.10681</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6084</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6080</t>
         </is>
       </c>
     </row>
@@ -7780,11 +7780,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Commingled Souris River &amp; Deadwood Formations Helium Production Well [101/11-34-002-26W3/04] (NAH Battle Creek DD 1C11-34-2B14-34-2-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/09-31-003-26W3/00] (North American Helium Battle Creek 9-31-3-26)</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6086</v>
+        <v>6002</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -7833,14 +7833,14 @@
         <v>30</v>
       </c>
       <c r="V105" t="n">
-        <v>49.17016</v>
+        <v>49.25465</v>
       </c>
       <c r="W105" t="n">
-        <v>-109.40476</v>
+        <v>-109.48226</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6086</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6002</t>
         </is>
       </c>
     </row>
@@ -7850,11 +7850,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [121/07-09-017-14W3/00] (Gulf Sask Landing Wilhelm 7 9 17 14)</t>
+          <t>Deadwood Formation Helium Production Well [101/14-03-017-14W3/00] (Canadian Helium Wilhelm 14-3-17-14)</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6088</v>
+        <v>6021</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I106" t="b">
@@ -7903,14 +7903,14 @@
         <v>30</v>
       </c>
       <c r="V106" t="n">
-        <v>50.41642</v>
+        <v>50.41137</v>
       </c>
       <c r="W106" t="n">
-        <v>-107.87088</v>
+        <v>-107.85382</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6088</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6021</t>
         </is>
       </c>
     </row>
@@ -7920,11 +7920,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Fusilier North Mine</t>
+          <t>Deadwood Formation Helium Production Well [102/01-09-017-14W3/00] (B.A. Wilhelm 1 A 9)</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4331</v>
+        <v>5550</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sodium Sulphate</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7973,14 +7973,14 @@
         <v>30</v>
       </c>
       <c r="V107" t="n">
-        <v>51.91661</v>
+        <v>50.41339</v>
       </c>
       <c r="W107" t="n">
-        <v>-109.79822</v>
+        <v>-107.86357</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/4331</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
         </is>
       </c>
     </row>
@@ -7990,11 +7990,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [141/02-09-017-14W3/00] (IAC Wilhelm 2-9-17-14)</t>
+          <t>Deadwood Formation Helium Production Well [101/16-14-004-09W3/00] (NAH Mankota West DD 4A16-14-1C16-14-4-9)</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5549</v>
+        <v>6019</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -8043,14 +8043,14 @@
         <v>30</v>
       </c>
       <c r="V108" t="n">
-        <v>50.41544</v>
+        <v>49.30389</v>
       </c>
       <c r="W108" t="n">
-        <v>-107.86935</v>
+        <v>-107.10893</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6019</t>
         </is>
       </c>
     </row>
@@ -8060,11 +8060,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deadwood Formation Helium Production Well [102/01-09-017-14W3/00] (B.A. Wilhelm 1 A 9)</t>
+          <t>Deadwood Formation Helium Production Well [141/02-09-017-14W3/00] (IAC Wilhelm 2-9-17-14)</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5550</v>
+        <v>5549</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Deposit: Post-Production</t>
+          <t>Deposit: Production</t>
         </is>
       </c>
       <c r="I109" t="b">
@@ -8113,14 +8113,14 @@
         <v>30</v>
       </c>
       <c r="V109" t="n">
-        <v>50.41339</v>
+        <v>50.41544</v>
       </c>
       <c r="W109" t="n">
-        <v>-107.86357</v>
+        <v>-107.86935</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5550</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5549</t>
         </is>
       </c>
     </row>
@@ -8130,11 +8130,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Souris River Formation Helium Production Well [141/05-31-003-26W3/00] (Interex Battle Creek West 5-31-3-26)</t>
+          <t>Deadwood Formation Helium Production Well [101/12-25-004-09W3/00] (NAH Mankota DD 4D8-26-1B12-25-4-9)</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5558</v>
+        <v>6020</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -8183,14 +8183,14 @@
         <v>30</v>
       </c>
       <c r="V110" t="n">
-        <v>49.25304</v>
+        <v>49.32802</v>
       </c>
       <c r="W110" t="n">
-        <v>-109.50042</v>
+        <v>-107.10274</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/5558</t>
+          <t>https://mineraldeposits.saskatchewan.ca/Home/Viewdetails/6020</t>
         </is>
       </c>
     </row>
